--- a/excel/Weekends_2027年度予算_社長用.xlsx
+++ b/excel/Weekends_2027年度予算_社長用.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yataka-02\AppData\Local\Temp\claude\C--Users-yataka-02-Desktop-Claude\76fa42a7-01fc-42d8-86c7-11cf90447c56\scratchpad\margin-calculator\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619C745D-295B-479C-BB68-D891DF3C596D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63F18EE-523B-4299-9F48-C4DDDC59072D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="117">
   <si>
     <t>Weekends 2027年度　月別の目標と損益（2026年8月〜2027年7月）</t>
   </si>
@@ -93,6 +93,10 @@
 （105%）</t>
   </si>
   <si>
+    <t>販管費
+（100%達成時）</t>
+  </si>
+  <si>
     <t>営業利益
 （100%達成時）</t>
   </si>
@@ -157,7 +161,7 @@
     <t>・売上目標と粗利目標は、店長がスマレジに登録した予算の比率で配分し、売上は10万円単位、粗利は5万円単位に丸めた（年計を予算に合わせてある。目標を手で変えたら「年間目標との差」を0にする）。</t>
   </si>
   <si>
-    <t>・営業利益は、その月の粗利目標をちょうど達成し報奨金3万円を払った場合。固定費（人件費・テナント固定分・その他の店舗経費・共通部の費用）は12等分した。</t>
+    <t>・販管費と営業利益は、その月の粗利目標をちょうど達成し報奨金3万円を払った場合。販管費＝固定費（人件費・テナント固定分・その他の店舗経費・共通部の費用を12等分、月137.9万円）＋報奨金3万円＋テナント歩合（売上×6.92%）。内訳は「年間損益」シートの「4. 1か月の販管費」。</t>
   </si>
   <si>
     <t>・報奨金は、その月の粗利が粗利目標の100%以上で店舗計3万円、105%以上で5万円。1人あたりの額は「年間損益」シートの「2. 報奨金のルール」。</t>
@@ -355,6 +359,51 @@
   </si>
   <si>
     <t>人件費＋テナント固定分＋その他の店舗経費＋共通部の費用</t>
+  </si>
+  <si>
+    <t>4. 1か月の販管費（全月100%達成の場合）</t>
+  </si>
+  <si>
+    <t>1か月</t>
+  </si>
+  <si>
+    <t>年間</t>
+  </si>
+  <si>
+    <t>決まり方</t>
+  </si>
+  <si>
+    <t>毎月同じ（賞与も12等分して含めている）</t>
+  </si>
+  <si>
+    <t>粗利目標を達成した月だけ。105%以上なら5万円</t>
+  </si>
+  <si>
+    <t>テナント経費（固定分）</t>
+  </si>
+  <si>
+    <t>毎月同じ</t>
+  </si>
+  <si>
+    <t>テナント経費（売上歩合）</t>
+  </si>
+  <si>
+    <t>売上×6.92%。月の売上で変わる（ここは12か月の平均。月別は「月別目標」シートの販管費の列）</t>
+  </si>
+  <si>
+    <t>毎月同じ（前年実績の12等分）</t>
+  </si>
+  <si>
+    <t>毎月同じ（前年は3月・7月の租税公課に集中。12等分している）</t>
+  </si>
+  <si>
+    <t>年間は「1. 年間の損益」の販管費 計（100%達成）と同じ</t>
+  </si>
+  <si>
+    <t>参考：前年実績（月平均）</t>
+  </si>
+  <si>
+    <t>前年は月119万円（8月）〜234万円（7月）。賞与（12月・7月）と租税公課（3月・7月）の月に増える</t>
   </si>
 </sst>
 </file>
@@ -498,7 +547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -546,6 +595,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -854,27 +904,29 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="9" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="9" width="15" customWidth="1"/>
+    <col min="10" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.600000000000001">
+    <row r="1" spans="1:13" ht="18.600000000000001">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15">
+    <row r="2" spans="1:13" ht="15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="49.95" customHeight="1">
+    <row r="3" spans="1:13" ht="49.95" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -897,7 +949,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="24" customHeight="1">
+    <row r="4" spans="1:13" ht="24" customHeight="1">
       <c r="A4" s="4">
         <f>年間損益!C6</f>
         <v>63000000</v>
@@ -927,7 +979,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="52.05" customHeight="1">
+    <row r="6" spans="1:13" ht="52.05" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
@@ -964,10 +1016,13 @@
       <c r="L6" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="15">
+      <c r="M6" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15">
       <c r="A7" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="8">
         <v>3040292</v>
@@ -990,26 +1045,30 @@
         <v>1300000</v>
       </c>
       <c r="H7" s="8">
-        <f>F7-E7*年間損益!$B$34-年間損益!$B$39/12-年間損益!$C$25</f>
+        <f>E7*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1665592</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" ref="I7:I18" si="1">F7-H7</f>
         <v>-415592</v>
       </c>
-      <c r="I7" s="8">
-        <f>SUM($H$7:H7)</f>
+      <c r="J7" s="8">
+        <f>SUM($I$7:I7)</f>
         <v>-415592</v>
       </c>
-      <c r="J7" s="10"/>
-      <c r="K7" s="9" t="str">
-        <f t="shared" ref="K7:K18" si="1">IF(J7="","",J7/F7)</f>
-        <v/>
-      </c>
-      <c r="L7" s="8" t="str">
-        <f>IF(J7="","",IF(J7&gt;=G7,年間損益!$D$25,IF(J7&gt;=F7,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15">
+      <c r="K7" s="10"/>
+      <c r="L7" s="9" t="str">
+        <f t="shared" ref="L7:L18" si="2">IF(K7="","",K7/F7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="8" t="str">
+        <f>IF(K7="","",IF(K7&gt;=G7,年間損益!$D$25,IF(K7&gt;=F7,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15">
       <c r="A8" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="8">
         <v>3638478</v>
@@ -1032,26 +1091,30 @@
         <v>1700000</v>
       </c>
       <c r="H8" s="8">
-        <f>F8-E8*年間損益!$B$34-年間損益!$B$39/12-年間損益!$C$25</f>
+        <f>E8*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1734792</v>
+      </c>
+      <c r="I8" s="8">
+        <f t="shared" si="1"/>
         <v>-134792</v>
       </c>
-      <c r="I8" s="8">
-        <f>SUM($H$7:H8)</f>
+      <c r="J8" s="8">
+        <f>SUM($I$7:I8)</f>
         <v>-550384</v>
       </c>
-      <c r="J8" s="10"/>
-      <c r="K8" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L8" s="8" t="str">
-        <f>IF(J8="","",IF(J8&gt;=G8,年間損益!$D$25,IF(J8&gt;=F8,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15">
+      <c r="K8" s="10"/>
+      <c r="L8" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M8" s="8" t="str">
+        <f>IF(K8="","",IF(K8&gt;=G8,年間損益!$D$25,IF(K8&gt;=F8,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15">
       <c r="A9" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="8">
         <v>4934704</v>
@@ -1074,26 +1137,30 @@
         <v>2100000</v>
       </c>
       <c r="H9" s="8">
-        <f>F9-E9*年間損益!$B$34-年間損益!$B$39/12-年間損益!$C$25</f>
+        <f>E9*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1810912</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="1"/>
         <v>189088</v>
       </c>
-      <c r="I9" s="8">
-        <f>SUM($H$7:H9)</f>
+      <c r="J9" s="8">
+        <f>SUM($I$7:I9)</f>
         <v>-361296</v>
       </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L9" s="8" t="str">
-        <f>IF(J9="","",IF(J9&gt;=G9,年間損益!$D$25,IF(J9&gt;=F9,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15">
+      <c r="K9" s="10"/>
+      <c r="L9" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M9" s="8" t="str">
+        <f>IF(K9="","",IF(K9&gt;=G9,年間損益!$D$25,IF(K9&gt;=F9,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15">
       <c r="A10" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="8">
         <v>5149749</v>
@@ -1116,26 +1183,30 @@
         <v>2100000</v>
       </c>
       <c r="H10" s="8">
-        <f>F10-E10*年間損益!$B$34-年間損益!$B$39/12-年間損益!$C$25</f>
+        <f>E10*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1810912</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="1"/>
         <v>189088</v>
       </c>
-      <c r="I10" s="8">
-        <f>SUM($H$7:H10)</f>
+      <c r="J10" s="8">
+        <f>SUM($I$7:I10)</f>
         <v>-172208</v>
       </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L10" s="8" t="str">
-        <f>IF(J10="","",IF(J10&gt;=G10,年間損益!$D$25,IF(J10&gt;=F10,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15">
+      <c r="K10" s="10"/>
+      <c r="L10" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M10" s="8" t="str">
+        <f>IF(K10="","",IF(K10&gt;=G10,年間損益!$D$25,IF(K10&gt;=F10,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15">
       <c r="A11" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="8">
         <v>6820952</v>
@@ -1158,26 +1229,30 @@
         <v>2650000</v>
       </c>
       <c r="H11" s="8">
-        <f>F11-E11*年間損益!$B$34-年間損益!$B$39/12-年間損益!$C$25</f>
+        <f>E11*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1914712</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="1"/>
         <v>585288</v>
       </c>
-      <c r="I11" s="8">
-        <f>SUM($H$7:H11)</f>
+      <c r="J11" s="8">
+        <f>SUM($I$7:I11)</f>
         <v>413080</v>
       </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L11" s="8" t="str">
-        <f>IF(J11="","",IF(J11&gt;=G11,年間損益!$D$25,IF(J11&gt;=F11,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15">
+      <c r="K11" s="10"/>
+      <c r="L11" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M11" s="8" t="str">
+        <f>IF(K11="","",IF(K11&gt;=G11,年間損益!$D$25,IF(K11&gt;=F11,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15">
       <c r="A12" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" s="8">
         <v>4850701</v>
@@ -1200,26 +1275,30 @@
         <v>2200000</v>
       </c>
       <c r="H12" s="8">
-        <f>F12-E12*年間損益!$B$34-年間損益!$B$39/12-年間損益!$C$25</f>
+        <f>E12*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1845512</v>
+      </c>
+      <c r="I12" s="8">
+        <f t="shared" si="1"/>
         <v>254488</v>
       </c>
-      <c r="I12" s="8">
-        <f>SUM($H$7:H12)</f>
+      <c r="J12" s="8">
+        <f>SUM($I$7:I12)</f>
         <v>667568</v>
       </c>
-      <c r="J12" s="10"/>
-      <c r="K12" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L12" s="8" t="str">
-        <f>IF(J12="","",IF(J12&gt;=G12,年間損益!$D$25,IF(J12&gt;=F12,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15">
+      <c r="K12" s="10"/>
+      <c r="L12" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M12" s="8" t="str">
+        <f>IF(K12="","",IF(K12&gt;=G12,年間損益!$D$25,IF(K12&gt;=F12,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15">
       <c r="A13" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" s="8">
         <v>2795656</v>
@@ -1242,26 +1321,30 @@
         <v>1300000</v>
       </c>
       <c r="H13" s="8">
-        <f>F13-E13*年間損益!$B$34-年間損益!$B$39/12-年間損益!$C$25</f>
+        <f>E13*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1665592</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="1"/>
         <v>-415592</v>
       </c>
-      <c r="I13" s="8">
-        <f>SUM($H$7:H13)</f>
+      <c r="J13" s="8">
+        <f>SUM($I$7:I13)</f>
         <v>251976</v>
       </c>
-      <c r="J13" s="10"/>
-      <c r="K13" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L13" s="8" t="str">
-        <f>IF(J13="","",IF(J13&gt;=G13,年間損益!$D$25,IF(J13&gt;=F13,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15">
+      <c r="K13" s="10"/>
+      <c r="L13" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M13" s="8" t="str">
+        <f>IF(K13="","",IF(K13&gt;=G13,年間損益!$D$25,IF(K13&gt;=F13,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15">
       <c r="A14" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="8">
         <v>4419804</v>
@@ -1284,26 +1367,30 @@
         <v>2100000</v>
       </c>
       <c r="H14" s="8">
-        <f>F14-E14*年間損益!$B$34-年間損益!$B$39/12-年間損益!$C$25</f>
+        <f>E14*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1810912</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="1"/>
         <v>189088</v>
       </c>
-      <c r="I14" s="8">
-        <f>SUM($H$7:H14)</f>
+      <c r="J14" s="8">
+        <f>SUM($I$7:I14)</f>
         <v>441064</v>
       </c>
-      <c r="J14" s="10"/>
-      <c r="K14" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L14" s="8" t="str">
-        <f>IF(J14="","",IF(J14&gt;=G14,年間損益!$D$25,IF(J14&gt;=F14,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15">
+      <c r="K14" s="10"/>
+      <c r="L14" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M14" s="8" t="str">
+        <f>IF(K14="","",IF(K14&gt;=G14,年間損益!$D$25,IF(K14&gt;=F14,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15">
       <c r="A15" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="8">
         <v>3581469</v>
@@ -1326,26 +1413,30 @@
         <v>1700000</v>
       </c>
       <c r="H15" s="8">
-        <f>F15-E15*年間損益!$B$34-年間損益!$B$39/12-年間損益!$C$25</f>
+        <f>E15*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1734792</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="1"/>
         <v>-134792</v>
       </c>
-      <c r="I15" s="8">
-        <f>SUM($H$7:H15)</f>
+      <c r="J15" s="8">
+        <f>SUM($I$7:I15)</f>
         <v>306272</v>
       </c>
-      <c r="J15" s="10"/>
-      <c r="K15" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L15" s="8" t="str">
-        <f>IF(J15="","",IF(J15&gt;=G15,年間損益!$D$25,IF(J15&gt;=F15,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15">
+      <c r="K15" s="10"/>
+      <c r="L15" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M15" s="8" t="str">
+        <f>IF(K15="","",IF(K15&gt;=G15,年間損益!$D$25,IF(K15&gt;=F15,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15">
       <c r="A16" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="8">
         <v>4799124</v>
@@ -1368,26 +1459,30 @@
         <v>1700000</v>
       </c>
       <c r="H16" s="8">
-        <f>F16-E16*年間損益!$B$34-年間損益!$B$39/12-年間損益!$C$25</f>
+        <f>E16*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1734792</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="1"/>
         <v>-134792</v>
       </c>
-      <c r="I16" s="8">
-        <f>SUM($H$7:H16)</f>
+      <c r="J16" s="8">
+        <f>SUM($I$7:I16)</f>
         <v>171480</v>
       </c>
-      <c r="J16" s="10"/>
-      <c r="K16" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L16" s="8" t="str">
-        <f>IF(J16="","",IF(J16&gt;=G16,年間損益!$D$25,IF(J16&gt;=F16,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="15">
+      <c r="K16" s="10"/>
+      <c r="L16" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M16" s="8" t="str">
+        <f>IF(K16="","",IF(K16&gt;=G16,年間損益!$D$25,IF(K16&gt;=F16,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15">
       <c r="A17" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17" s="8">
         <v>4888307</v>
@@ -1410,26 +1505,30 @@
         <v>2100000</v>
       </c>
       <c r="H17" s="8">
-        <f>F17-E17*年間損益!$B$34-年間損益!$B$39/12-年間損益!$C$25</f>
+        <f>E17*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1810912</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="1"/>
         <v>189088</v>
       </c>
-      <c r="I17" s="8">
-        <f>SUM($H$7:H17)</f>
+      <c r="J17" s="8">
+        <f>SUM($I$7:I17)</f>
         <v>360568</v>
       </c>
-      <c r="J17" s="10"/>
-      <c r="K17" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L17" s="8" t="str">
-        <f>IF(J17="","",IF(J17&gt;=G17,年間損益!$D$25,IF(J17&gt;=F17,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="15">
+      <c r="K17" s="10"/>
+      <c r="L17" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M17" s="8" t="str">
+        <f>IF(K17="","",IF(K17&gt;=G17,年間損益!$D$25,IF(K17&gt;=F17,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15">
       <c r="A18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" s="8">
         <v>4741065</v>
@@ -1452,72 +1551,80 @@
         <v>1700000</v>
       </c>
       <c r="H18" s="8">
-        <f>F18-E18*年間損益!$B$34-年間損益!$B$39/12-年間損益!$C$25</f>
+        <f>E18*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1734792</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="1"/>
         <v>-134792</v>
       </c>
-      <c r="I18" s="8">
-        <f>SUM($H$7:H18)</f>
+      <c r="J18" s="8">
+        <f>SUM($I$7:I18)</f>
         <v>225776</v>
       </c>
-      <c r="J18" s="10"/>
-      <c r="K18" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L18" s="8" t="str">
-        <f>IF(J18="","",IF(J18&gt;=G18,年間損益!$D$25,IF(J18&gt;=F18,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="15">
+      <c r="K18" s="10"/>
+      <c r="L18" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M18" s="8" t="str">
+        <f>IF(K18="","",IF(K18&gt;=G18,年間損益!$D$25,IF(K18&gt;=F18,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15">
       <c r="A19" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="12">
-        <f t="shared" ref="B19:H19" si="2">SUM(B7:B18)</f>
+        <f t="shared" ref="B19:I19" si="3">SUM(B7:B18)</f>
         <v>53660301</v>
       </c>
       <c r="C19" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60000000</v>
       </c>
       <c r="D19" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.99999999999999989</v>
       </c>
       <c r="E19" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>63000000</v>
       </c>
       <c r="F19" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>21500000</v>
       </c>
       <c r="G19" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>22650000</v>
       </c>
       <c r="H19" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
+        <v>21274224</v>
+      </c>
+      <c r="I19" s="12">
+        <f t="shared" si="3"/>
         <v>225776</v>
       </c>
-      <c r="I19" s="14"/>
-      <c r="J19" s="12">
-        <f>SUM(J7:J18)</f>
+      <c r="J19" s="14"/>
+      <c r="K19" s="12">
+        <f>SUM(K7:K18)</f>
         <v>0</v>
       </c>
-      <c r="K19" s="13" t="str">
-        <f>IF(COUNT(J7:J18)=0,"",J19/SUMIF(J7:J18,"&lt;&gt;",F7:F18))</f>
-        <v/>
-      </c>
-      <c r="L19" s="12">
-        <f>SUM(L7:L18)</f>
+      <c r="L19" s="13" t="str">
+        <f>IF(COUNT(K7:K18)=0,"",K19/SUMIF(K7:K18,"&lt;&gt;",F7:F18))</f>
+        <v/>
+      </c>
+      <c r="M19" s="12">
+        <f>SUM(M7:M18)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15">
+    <row r="20" spans="1:13" ht="15">
       <c r="A20" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E20" s="8">
         <f>E19-年間損益!B30</f>
@@ -1528,29 +1635,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15">
+    <row r="22" spans="1:13" ht="15">
       <c r="A22" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="15">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15">
       <c r="A23" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="15">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15">
       <c r="A24" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="15">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15">
       <c r="A25" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="15">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15">
       <c r="A26" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1565,7 +1672,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -1575,39 +1682,39 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.600000000000001">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="49.95" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15">
       <c r="A6" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" s="8">
         <v>53660301</v>
@@ -1621,12 +1728,12 @@
         <v>66150000</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15">
       <c r="A7" s="18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" s="12">
         <v>16612146</v>
@@ -1640,7 +1747,7 @@
         <v>22575000</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15">
@@ -1663,7 +1770,7 @@
     </row>
     <row r="9" spans="1:5" ht="15">
       <c r="A9" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" s="8">
         <v>8091567</v>
@@ -1677,12 +1784,12 @@
         <v>9600000</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10" s="8">
         <v>0</v>
@@ -1696,12 +1803,12 @@
         <v>600000</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
       <c r="A11" s="16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" s="8">
         <v>6230261</v>
@@ -1715,12 +1822,12 @@
         <v>7095084</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15">
       <c r="A12" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B12" s="8">
         <v>3493268</v>
@@ -1734,12 +1841,12 @@
         <v>3493268</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15">
       <c r="A13" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="8">
         <v>943852</v>
@@ -1753,12 +1860,12 @@
         <v>943852</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15">
       <c r="A14" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" s="8">
         <f>SUM(B9:B13)</f>
@@ -1776,7 +1883,7 @@
     </row>
     <row r="15" spans="1:5" ht="15">
       <c r="A15" s="18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="12">
         <f>B7-B14</f>
@@ -1794,7 +1901,7 @@
     </row>
     <row r="16" spans="1:5" ht="30">
       <c r="A16" s="16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" s="8">
         <v>-153129</v>
@@ -1808,12 +1915,12 @@
         <v>-300000</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15">
       <c r="A17" s="18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="12">
         <f>B15+B16</f>
@@ -1831,7 +1938,7 @@
     </row>
     <row r="18" spans="1:5" ht="15">
       <c r="A18" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8">
@@ -1843,31 +1950,31 @@
         <v>60846964.598259076</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15">
       <c r="A20" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="49.95" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15">
       <c r="A22" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B22" s="20">
         <v>1</v>
@@ -1881,7 +1988,7 @@
     </row>
     <row r="23" spans="1:5" ht="15">
       <c r="A23" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B23" s="20">
         <v>1</v>
@@ -1895,7 +2002,7 @@
     </row>
     <row r="24" spans="1:5" ht="15">
       <c r="A24" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B24" s="20">
         <v>2</v>
@@ -1909,7 +2016,7 @@
     </row>
     <row r="25" spans="1:5" ht="15">
       <c r="A25" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B25" s="21">
         <f>SUM(B22:B24)</f>
@@ -1926,7 +2033,7 @@
     </row>
     <row r="26" spans="1:5" ht="15">
       <c r="A26" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="8">
@@ -1940,18 +2047,18 @@
     </row>
     <row r="28" spans="1:5" ht="15">
       <c r="A28" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15">
       <c r="A29" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" s="27" t="s">
         <v>82</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>83</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="26"/>
@@ -1964,7 +2071,7 @@
         <v>63000000</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D30" s="25"/>
       <c r="E30" s="26"/>
@@ -1977,129 +2084,294 @@
         <v>21500000</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D31" s="25"/>
       <c r="E31" s="26"/>
     </row>
     <row r="32" spans="1:5" ht="15">
       <c r="A32" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B32" s="10">
         <v>800000</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D32" s="25"/>
       <c r="E32" s="26"/>
     </row>
     <row r="33" spans="1:5" ht="15">
       <c r="A33" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B33" s="10">
         <v>209792</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D33" s="25"/>
       <c r="E33" s="26"/>
     </row>
     <row r="34" spans="1:5" ht="15">
       <c r="A34" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B34" s="22">
         <v>6.9199999999999998E-2</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D34" s="25"/>
       <c r="E34" s="26"/>
     </row>
     <row r="35" spans="1:5" ht="15">
       <c r="A35" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B35" s="10">
         <v>3493268</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D35" s="25"/>
       <c r="E35" s="26"/>
     </row>
     <row r="36" spans="1:5" ht="15">
       <c r="A36" s="16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B36" s="10">
         <v>943852</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="26"/>
     </row>
     <row r="37" spans="1:5" ht="15">
       <c r="A37" s="16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B37" s="10">
         <v>300000</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D37" s="25"/>
       <c r="E37" s="26"/>
     </row>
     <row r="38" spans="1:5" ht="15">
       <c r="A38" s="16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B38" s="23">
         <v>1.05</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D38" s="25"/>
       <c r="E38" s="26"/>
     </row>
     <row r="39" spans="1:5" ht="15">
       <c r="A39" s="16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B39" s="8">
         <f>B32*12+B33*12+B35+B36</f>
         <v>16554624</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D39" s="25"/>
       <c r="E39" s="26"/>
     </row>
+    <row r="41" spans="1:5" ht="15">
+      <c r="A41" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15">
+      <c r="A42" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="E42" s="26"/>
+    </row>
+    <row r="43" spans="1:5" ht="15">
+      <c r="A43" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="8">
+        <f>$B$32</f>
+        <v>800000</v>
+      </c>
+      <c r="C43" s="8">
+        <f t="shared" ref="C43:C48" si="0">B43*12</f>
+        <v>9600000</v>
+      </c>
+      <c r="D43" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="E43" s="26"/>
+    </row>
+    <row r="44" spans="1:5" ht="15">
+      <c r="A44" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="8">
+        <f>$C$25</f>
+        <v>30000</v>
+      </c>
+      <c r="C44" s="8">
+        <f t="shared" si="0"/>
+        <v>360000</v>
+      </c>
+      <c r="D44" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="E44" s="26"/>
+    </row>
+    <row r="45" spans="1:5" ht="15">
+      <c r="A45" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B45" s="8">
+        <f>$B$33</f>
+        <v>209792</v>
+      </c>
+      <c r="C45" s="8">
+        <f t="shared" si="0"/>
+        <v>2517504</v>
+      </c>
+      <c r="D45" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="E45" s="26"/>
+    </row>
+    <row r="46" spans="1:5" ht="15">
+      <c r="A46" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B46" s="8">
+        <f>$B$30*$B$34/12</f>
+        <v>363300</v>
+      </c>
+      <c r="C46" s="8">
+        <f t="shared" si="0"/>
+        <v>4359600</v>
+      </c>
+      <c r="D46" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="E46" s="26"/>
+    </row>
+    <row r="47" spans="1:5" ht="15">
+      <c r="A47" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" s="8">
+        <f>$B$35/12</f>
+        <v>291105.66666666669</v>
+      </c>
+      <c r="C47" s="8">
+        <f t="shared" si="0"/>
+        <v>3493268</v>
+      </c>
+      <c r="D47" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="E47" s="26"/>
+    </row>
+    <row r="48" spans="1:5" ht="15">
+      <c r="A48" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="8">
+        <f>$B$36/12</f>
+        <v>78654.333333333328</v>
+      </c>
+      <c r="C48" s="8">
+        <f t="shared" si="0"/>
+        <v>943852</v>
+      </c>
+      <c r="D48" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="E48" s="26"/>
+    </row>
+    <row r="49" spans="1:5" ht="15">
+      <c r="A49" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="12">
+        <f>SUM(B43:B48)</f>
+        <v>1772852</v>
+      </c>
+      <c r="C49" s="12">
+        <f>SUM(C43:C48)</f>
+        <v>21274224</v>
+      </c>
+      <c r="D49" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="E49" s="26"/>
+    </row>
+    <row r="50" spans="1:5" ht="15">
+      <c r="A50" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B50" s="8">
+        <f>B14/12</f>
+        <v>1563245.6666666667</v>
+      </c>
+      <c r="C50" s="8">
+        <f>B14</f>
+        <v>18758948</v>
+      </c>
+      <c r="D50" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="E50" s="26"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="20">
     <mergeCell ref="C29:E29"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D44:E44"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="D42:E42"/>
     <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="D48:E48"/>
     <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="D47:E47"/>
     <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="D43:E43"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/Weekends_2027年度予算_社長用.xlsx
+++ b/excel/Weekends_2027年度予算_社長用.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yataka-02\AppData\Local\Temp\claude\C--Users-yataka-02-Desktop-Claude\76fa42a7-01fc-42d8-86c7-11cf90447c56\scratchpad\margin-calculator\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63F18EE-523B-4299-9F48-C4DDDC59072D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBA0CE1-8426-4735-BD2F-86232BBF47E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="118">
   <si>
     <t>Weekends 2027年度　月別の目標と損益（2026年8月〜2027年7月）</t>
   </si>
@@ -158,7 +158,10 @@
     <t>年間目標との差</t>
   </si>
   <si>
-    <t>・売上目標と粗利目標は、店長がスマレジに登録した予算の比率で配分し、売上は10万円単位、粗利は5万円単位に丸めた（年計を予算に合わせてある。目標を手で変えたら「年間目標との差」を0にする）。</t>
+    <t>・売上目標と粗利目標は、店長がスマレジに登録した予算の比率で配分し、売上は10万円単位、粗利は5万円単位に丸めた。</t>
+  </si>
+  <si>
+    <t>・そのうえで、どの月も営業利益がマイナスにならないよう、閑散月（8・9・2・4・5・7月）を粗利180万円・売上530万円に引き上げた（毎月の販管費を賄うのに必要な粗利は約177万円）。目標を手で変えたら「年間目標との差」を0にする。</t>
   </si>
   <si>
     <t>・販管費と営業利益は、その月の粗利目標をちょうど達成し報奨金3万円を払った場合。販管費＝固定費（人件費・テナント固定分・その他の店舗経費・共通部の費用を12等分、月137.9万円）＋報奨金3万円＋テナント歩合（売上×6.92%）。内訳は「年間損益」シートの「4. 1か月の販管費」。</t>
@@ -167,7 +170,7 @@
     <t>・報奨金は、その月の粗利が粗利目標の100%以上で店舗計3万円、105%以上で5万円。1人あたりの額は「年間損益」シートの「2. 報奨金のルール」。</t>
   </si>
   <si>
-    <t>・105%の粗利目標は月ごとに5万円単位で丸めたため、年計は2,265万円（2,150万円×105%＝2,257.5万円より7.5万円多い）。「年間損益」シートの105%欄は丸める前の2,257.5万円で計算している。</t>
+    <t>・105%の粗利目標は月ごとに5万円単位で丸めたため、年計は「年間損益」シートの105%欄（粗利目標×105%）と少しずれる。</t>
   </si>
   <si>
     <t>・達成率の年計は、実績を入れた月だけで計算する。</t>
@@ -203,7 +206,7 @@
     <t>売上高</t>
   </si>
   <si>
-    <t>予算は年6,300万円。105%は売上も5%増えた場合</t>
+    <t>予算は年6,860万円。105%は売上も5%増えた場合</t>
   </si>
   <si>
     <t>売上総利益（粗利）</t>
@@ -307,10 +310,10 @@
     <t>出所・備考</t>
   </si>
   <si>
-    <t>検討案</t>
-  </si>
-  <si>
-    <t>検討案（粗利率34.1%）</t>
+    <t>毎月黒字の案（2026-10-06。旧案は6,300万円）</t>
+  </si>
+  <si>
+    <t>毎月黒字の案（粗利率34.1%。旧案は2,150万円）</t>
   </si>
   <si>
     <t>人件費（月）</t>
@@ -592,13 +595,13 @@
     </xf>
     <xf numFmtId="10" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -904,7 +907,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -952,23 +955,23 @@
     <row r="4" spans="1:13" ht="24" customHeight="1">
       <c r="A4" s="4">
         <f>年間損益!C6</f>
-        <v>63000000</v>
+        <v>68600000</v>
       </c>
       <c r="B4" s="4">
         <f>年間損益!C7</f>
-        <v>21500000</v>
+        <v>23400000</v>
       </c>
       <c r="C4" s="5">
         <f>年間損益!C8</f>
-        <v>0.34126984126984128</v>
+        <v>0.34110787172011664</v>
       </c>
       <c r="D4" s="4">
         <f>年間損益!C15</f>
-        <v>225776</v>
+        <v>1738256</v>
       </c>
       <c r="E4" s="4">
         <f>年間損益!D15</f>
-        <v>842796</v>
+        <v>2430900</v>
       </c>
       <c r="F4" s="4">
         <f>年間損益!C10</f>
@@ -1035,26 +1038,26 @@
         <v>5.8333333333333334E-2</v>
       </c>
       <c r="E7" s="10">
-        <v>3700000</v>
+        <v>5300000</v>
       </c>
       <c r="F7" s="10">
-        <v>1250000</v>
+        <v>1800000</v>
       </c>
       <c r="G7" s="8">
         <f>ROUND(F7*年間損益!$B$38/50000,0)*50000</f>
-        <v>1300000</v>
+        <v>1900000</v>
       </c>
       <c r="H7" s="8">
         <f>E7*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1665592</v>
+        <v>1776312</v>
       </c>
       <c r="I7" s="8">
         <f t="shared" ref="I7:I18" si="1">F7-H7</f>
-        <v>-415592</v>
+        <v>23688</v>
       </c>
       <c r="J7" s="8">
         <f>SUM($I$7:I7)</f>
-        <v>-415592</v>
+        <v>23688</v>
       </c>
       <c r="K7" s="10"/>
       <c r="L7" s="9" t="str">
@@ -1081,26 +1084,26 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E8" s="10">
-        <v>4700000</v>
+        <v>5300000</v>
       </c>
       <c r="F8" s="10">
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="G8" s="8">
         <f>ROUND(F8*年間損益!$B$38/50000,0)*50000</f>
-        <v>1700000</v>
+        <v>1900000</v>
       </c>
       <c r="H8" s="8">
         <f>E8*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1734792</v>
+        <v>1776312</v>
       </c>
       <c r="I8" s="8">
         <f t="shared" si="1"/>
-        <v>-134792</v>
+        <v>23688</v>
       </c>
       <c r="J8" s="8">
         <f>SUM($I$7:I8)</f>
-        <v>-550384</v>
+        <v>47376</v>
       </c>
       <c r="K8" s="10"/>
       <c r="L8" s="9" t="str">
@@ -1146,7 +1149,7 @@
       </c>
       <c r="J9" s="8">
         <f>SUM($I$7:I9)</f>
-        <v>-361296</v>
+        <v>236464</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="9" t="str">
@@ -1192,7 +1195,7 @@
       </c>
       <c r="J10" s="8">
         <f>SUM($I$7:I10)</f>
-        <v>-172208</v>
+        <v>425552</v>
       </c>
       <c r="K10" s="10"/>
       <c r="L10" s="9" t="str">
@@ -1238,7 +1241,7 @@
       </c>
       <c r="J11" s="8">
         <f>SUM($I$7:I11)</f>
-        <v>413080</v>
+        <v>1010840</v>
       </c>
       <c r="K11" s="10"/>
       <c r="L11" s="9" t="str">
@@ -1284,7 +1287,7 @@
       </c>
       <c r="J12" s="8">
         <f>SUM($I$7:I12)</f>
-        <v>667568</v>
+        <v>1265328</v>
       </c>
       <c r="K12" s="10"/>
       <c r="L12" s="9" t="str">
@@ -1311,26 +1314,26 @@
         <v>5.8333333333333334E-2</v>
       </c>
       <c r="E13" s="10">
-        <v>3700000</v>
+        <v>5300000</v>
       </c>
       <c r="F13" s="10">
-        <v>1250000</v>
+        <v>1800000</v>
       </c>
       <c r="G13" s="8">
         <f>ROUND(F13*年間損益!$B$38/50000,0)*50000</f>
-        <v>1300000</v>
+        <v>1900000</v>
       </c>
       <c r="H13" s="8">
         <f>E13*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1665592</v>
+        <v>1776312</v>
       </c>
       <c r="I13" s="8">
         <f t="shared" si="1"/>
-        <v>-415592</v>
+        <v>23688</v>
       </c>
       <c r="J13" s="8">
         <f>SUM($I$7:I13)</f>
-        <v>251976</v>
+        <v>1289016</v>
       </c>
       <c r="K13" s="10"/>
       <c r="L13" s="9" t="str">
@@ -1376,7 +1379,7 @@
       </c>
       <c r="J14" s="8">
         <f>SUM($I$7:I14)</f>
-        <v>441064</v>
+        <v>1478104</v>
       </c>
       <c r="K14" s="10"/>
       <c r="L14" s="9" t="str">
@@ -1403,26 +1406,26 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E15" s="10">
-        <v>4700000</v>
+        <v>5300000</v>
       </c>
       <c r="F15" s="10">
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="G15" s="8">
         <f>ROUND(F15*年間損益!$B$38/50000,0)*50000</f>
-        <v>1700000</v>
+        <v>1900000</v>
       </c>
       <c r="H15" s="8">
         <f>E15*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1734792</v>
+        <v>1776312</v>
       </c>
       <c r="I15" s="8">
         <f t="shared" si="1"/>
-        <v>-134792</v>
+        <v>23688</v>
       </c>
       <c r="J15" s="8">
         <f>SUM($I$7:I15)</f>
-        <v>306272</v>
+        <v>1501792</v>
       </c>
       <c r="K15" s="10"/>
       <c r="L15" s="9" t="str">
@@ -1449,26 +1452,26 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E16" s="10">
-        <v>4700000</v>
+        <v>5300000</v>
       </c>
       <c r="F16" s="10">
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="G16" s="8">
         <f>ROUND(F16*年間損益!$B$38/50000,0)*50000</f>
-        <v>1700000</v>
+        <v>1900000</v>
       </c>
       <c r="H16" s="8">
         <f>E16*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1734792</v>
+        <v>1776312</v>
       </c>
       <c r="I16" s="8">
         <f t="shared" si="1"/>
-        <v>-134792</v>
+        <v>23688</v>
       </c>
       <c r="J16" s="8">
         <f>SUM($I$7:I16)</f>
-        <v>171480</v>
+        <v>1525480</v>
       </c>
       <c r="K16" s="10"/>
       <c r="L16" s="9" t="str">
@@ -1514,7 +1517,7 @@
       </c>
       <c r="J17" s="8">
         <f>SUM($I$7:I17)</f>
-        <v>360568</v>
+        <v>1714568</v>
       </c>
       <c r="K17" s="10"/>
       <c r="L17" s="9" t="str">
@@ -1541,26 +1544,26 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E18" s="10">
-        <v>4700000</v>
+        <v>5300000</v>
       </c>
       <c r="F18" s="10">
-        <v>1600000</v>
+        <v>1800000</v>
       </c>
       <c r="G18" s="8">
         <f>ROUND(F18*年間損益!$B$38/50000,0)*50000</f>
-        <v>1700000</v>
+        <v>1900000</v>
       </c>
       <c r="H18" s="8">
         <f>E18*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1734792</v>
+        <v>1776312</v>
       </c>
       <c r="I18" s="8">
         <f t="shared" si="1"/>
-        <v>-134792</v>
+        <v>23688</v>
       </c>
       <c r="J18" s="8">
         <f>SUM($I$7:I18)</f>
-        <v>225776</v>
+        <v>1738256</v>
       </c>
       <c r="K18" s="10"/>
       <c r="L18" s="9" t="str">
@@ -1590,23 +1593,23 @@
       </c>
       <c r="E19" s="12">
         <f t="shared" si="3"/>
-        <v>63000000</v>
+        <v>68600000</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="3"/>
-        <v>21500000</v>
+        <v>23400000</v>
       </c>
       <c r="G19" s="12">
         <f t="shared" si="3"/>
-        <v>22650000</v>
+        <v>24650000</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="3"/>
-        <v>21274224</v>
+        <v>21661744</v>
       </c>
       <c r="I19" s="12">
         <f t="shared" si="3"/>
-        <v>225776</v>
+        <v>1738256</v>
       </c>
       <c r="J19" s="14"/>
       <c r="K19" s="12">
@@ -1658,6 +1661,11 @@
     <row r="26" spans="1:13" ht="15">
       <c r="A26" s="2" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15">
+      <c r="A27" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1682,72 +1690,72 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.600000000000001">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="49.95" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15">
       <c r="A6" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="8">
         <v>53660301</v>
       </c>
       <c r="C6" s="8">
         <f>$B$30</f>
-        <v>63000000</v>
+        <v>68600000</v>
       </c>
       <c r="D6" s="8">
         <f>$B$30*$B$38</f>
-        <v>66150000</v>
+        <v>72030000</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15">
       <c r="A7" s="18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="12">
         <v>16612146</v>
       </c>
       <c r="C7" s="12">
         <f>$B$31</f>
-        <v>21500000</v>
+        <v>23400000</v>
       </c>
       <c r="D7" s="12">
         <f>$B$31*$B$38</f>
-        <v>22575000</v>
+        <v>24570000</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15">
@@ -1760,17 +1768,17 @@
       </c>
       <c r="C8" s="9">
         <f>C7/C6</f>
-        <v>0.34126984126984128</v>
+        <v>0.34110787172011664</v>
       </c>
       <c r="D8" s="9">
         <f>D7/D6</f>
-        <v>0.34126984126984128</v>
+        <v>0.34110787172011664</v>
       </c>
       <c r="E8" s="17"/>
     </row>
     <row r="9" spans="1:5" ht="15">
       <c r="A9" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" s="8">
         <v>8091567</v>
@@ -1784,12 +1792,12 @@
         <v>9600000</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" s="8">
         <v>0</v>
@@ -1803,31 +1811,31 @@
         <v>600000</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
       <c r="A11" s="16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" s="8">
         <v>6230261</v>
       </c>
       <c r="C11" s="8">
         <f>$B$33*12+C6*$B$34</f>
-        <v>6877104</v>
+        <v>7264624</v>
       </c>
       <c r="D11" s="8">
         <f>$B$33*12+D6*$B$34</f>
-        <v>7095084</v>
+        <v>7501980</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15">
       <c r="A12" s="16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="8">
         <v>3493268</v>
@@ -1841,12 +1849,12 @@
         <v>3493268</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15">
       <c r="A13" s="16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B13" s="8">
         <v>943852</v>
@@ -1860,12 +1868,12 @@
         <v>943852</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15">
       <c r="A14" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="8">
         <f>SUM(B9:B13)</f>
@@ -1873,17 +1881,17 @@
       </c>
       <c r="C14" s="8">
         <f>SUM(C9:C13)</f>
-        <v>21274224</v>
+        <v>21661744</v>
       </c>
       <c r="D14" s="8">
         <f>SUM(D9:D13)</f>
-        <v>21732204</v>
+        <v>22139100</v>
       </c>
       <c r="E14" s="17"/>
     </row>
     <row r="15" spans="1:5" ht="15">
       <c r="A15" s="18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" s="12">
         <f>B7-B14</f>
@@ -1891,17 +1899,17 @@
       </c>
       <c r="C15" s="12">
         <f>C7-C14</f>
-        <v>225776</v>
+        <v>1738256</v>
       </c>
       <c r="D15" s="12">
         <f>D7-D14</f>
-        <v>842796</v>
+        <v>2430900</v>
       </c>
       <c r="E15" s="19"/>
     </row>
     <row r="16" spans="1:5" ht="30">
       <c r="A16" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="8">
         <v>-153129</v>
@@ -1915,12 +1923,12 @@
         <v>-300000</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15">
       <c r="A17" s="18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" s="12">
         <f>B15+B16</f>
@@ -1928,53 +1936,53 @@
       </c>
       <c r="C17" s="12">
         <f>C15+C16</f>
-        <v>-74224</v>
+        <v>1438256</v>
       </c>
       <c r="D17" s="12">
         <f>D15+D16</f>
-        <v>542796</v>
+        <v>2130900</v>
       </c>
       <c r="E17" s="19"/>
     </row>
     <row r="18" spans="1:5" ht="15">
       <c r="A18" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8">
         <f>$B$39/($B$31/$B$30-$B$34)</f>
-        <v>60846964.598259076</v>
+        <v>60883209.79923743</v>
       </c>
       <c r="D18" s="8">
         <f>$B$39/($B$31/$B$30-$B$34)</f>
-        <v>60846964.598259076</v>
+        <v>60883209.79923743</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15">
       <c r="A20" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="49.95" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15">
       <c r="A22" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B22" s="20">
         <v>1</v>
@@ -1988,7 +1996,7 @@
     </row>
     <row r="23" spans="1:5" ht="15">
       <c r="A23" s="16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B23" s="20">
         <v>1</v>
@@ -2002,7 +2010,7 @@
     </row>
     <row r="24" spans="1:5" ht="15">
       <c r="A24" s="16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B24" s="20">
         <v>2</v>
@@ -2016,7 +2024,7 @@
     </row>
     <row r="25" spans="1:5" ht="15">
       <c r="A25" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B25" s="21">
         <f>SUM(B22:B24)</f>
@@ -2033,7 +2041,7 @@
     </row>
     <row r="26" spans="1:5" ht="15">
       <c r="A26" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="8">
@@ -2047,18 +2055,18 @@
     </row>
     <row r="28" spans="1:5" ht="15">
       <c r="A28" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15">
       <c r="A29" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C29" s="28" t="s">
         <v>83</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>84</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="26"/>
@@ -2068,10 +2076,10 @@
         <v>2</v>
       </c>
       <c r="B30" s="10">
-        <v>63000000</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>84</v>
+        <v>68600000</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>85</v>
       </c>
       <c r="D30" s="25"/>
       <c r="E30" s="26"/>
@@ -2081,142 +2089,142 @@
         <v>3</v>
       </c>
       <c r="B31" s="10">
-        <v>21500000</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>85</v>
+        <v>23400000</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>86</v>
       </c>
       <c r="D31" s="25"/>
       <c r="E31" s="26"/>
     </row>
     <row r="32" spans="1:5" ht="15">
       <c r="A32" s="16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B32" s="10">
         <v>800000</v>
       </c>
-      <c r="C32" s="24" t="s">
-        <v>87</v>
+      <c r="C32" s="27" t="s">
+        <v>88</v>
       </c>
       <c r="D32" s="25"/>
       <c r="E32" s="26"/>
     </row>
     <row r="33" spans="1:5" ht="15">
       <c r="A33" s="16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B33" s="10">
         <v>209792</v>
       </c>
-      <c r="C33" s="24" t="s">
-        <v>89</v>
+      <c r="C33" s="27" t="s">
+        <v>90</v>
       </c>
       <c r="D33" s="25"/>
       <c r="E33" s="26"/>
     </row>
     <row r="34" spans="1:5" ht="15">
       <c r="A34" s="16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B34" s="22">
         <v>6.9199999999999998E-2</v>
       </c>
-      <c r="C34" s="24" t="s">
-        <v>91</v>
+      <c r="C34" s="27" t="s">
+        <v>92</v>
       </c>
       <c r="D34" s="25"/>
       <c r="E34" s="26"/>
     </row>
     <row r="35" spans="1:5" ht="15">
       <c r="A35" s="16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B35" s="10">
         <v>3493268</v>
       </c>
-      <c r="C35" s="24" t="s">
-        <v>93</v>
+      <c r="C35" s="27" t="s">
+        <v>94</v>
       </c>
       <c r="D35" s="25"/>
       <c r="E35" s="26"/>
     </row>
     <row r="36" spans="1:5" ht="15">
       <c r="A36" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B36" s="10">
         <v>943852</v>
       </c>
-      <c r="C36" s="24" t="s">
-        <v>95</v>
+      <c r="C36" s="27" t="s">
+        <v>96</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="26"/>
     </row>
     <row r="37" spans="1:5" ht="15">
       <c r="A37" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B37" s="10">
         <v>300000</v>
       </c>
-      <c r="C37" s="24" t="s">
-        <v>97</v>
+      <c r="C37" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="D37" s="25"/>
       <c r="E37" s="26"/>
     </row>
     <row r="38" spans="1:5" ht="15">
       <c r="A38" s="16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B38" s="23">
         <v>1.05</v>
       </c>
-      <c r="C38" s="24" t="s">
-        <v>99</v>
+      <c r="C38" s="27" t="s">
+        <v>100</v>
       </c>
       <c r="D38" s="25"/>
       <c r="E38" s="26"/>
     </row>
     <row r="39" spans="1:5" ht="15">
       <c r="A39" s="16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B39" s="8">
         <f>B32*12+B33*12+B35+B36</f>
         <v>16554624</v>
       </c>
-      <c r="C39" s="24" t="s">
-        <v>101</v>
+      <c r="C39" s="27" t="s">
+        <v>102</v>
       </c>
       <c r="D39" s="25"/>
       <c r="E39" s="26"/>
     </row>
     <row r="41" spans="1:5" ht="15">
       <c r="A41" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15">
       <c r="A42" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D42" s="28" t="s">
         <v>105</v>
+      </c>
+      <c r="D42" s="24" t="s">
+        <v>106</v>
       </c>
       <c r="E42" s="26"/>
     </row>
     <row r="43" spans="1:5" ht="15">
       <c r="A43" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B43" s="8">
         <f>$B$32</f>
@@ -2226,14 +2234,14 @@
         <f t="shared" ref="C43:C48" si="0">B43*12</f>
         <v>9600000</v>
       </c>
-      <c r="D43" s="24" t="s">
-        <v>106</v>
+      <c r="D43" s="27" t="s">
+        <v>107</v>
       </c>
       <c r="E43" s="26"/>
     </row>
     <row r="44" spans="1:5" ht="15">
       <c r="A44" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B44" s="8">
         <f>$C$25</f>
@@ -2243,14 +2251,14 @@
         <f t="shared" si="0"/>
         <v>360000</v>
       </c>
-      <c r="D44" s="24" t="s">
-        <v>107</v>
+      <c r="D44" s="27" t="s">
+        <v>108</v>
       </c>
       <c r="E44" s="26"/>
     </row>
     <row r="45" spans="1:5" ht="15">
       <c r="A45" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B45" s="8">
         <f>$B$33</f>
@@ -2260,31 +2268,31 @@
         <f t="shared" si="0"/>
         <v>2517504</v>
       </c>
-      <c r="D45" s="24" t="s">
-        <v>109</v>
+      <c r="D45" s="27" t="s">
+        <v>110</v>
       </c>
       <c r="E45" s="26"/>
     </row>
     <row r="46" spans="1:5" ht="15">
       <c r="A46" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B46" s="8">
         <f>$B$30*$B$34/12</f>
-        <v>363300</v>
+        <v>395593.33333333331</v>
       </c>
       <c r="C46" s="8">
         <f t="shared" si="0"/>
-        <v>4359600</v>
-      </c>
-      <c r="D46" s="24" t="s">
-        <v>111</v>
+        <v>4747120</v>
+      </c>
+      <c r="D46" s="27" t="s">
+        <v>112</v>
       </c>
       <c r="E46" s="26"/>
     </row>
     <row r="47" spans="1:5" ht="15">
       <c r="A47" s="16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B47" s="8">
         <f>$B$35/12</f>
@@ -2294,14 +2302,14 @@
         <f t="shared" si="0"/>
         <v>3493268</v>
       </c>
-      <c r="D47" s="24" t="s">
-        <v>112</v>
+      <c r="D47" s="27" t="s">
+        <v>113</v>
       </c>
       <c r="E47" s="26"/>
     </row>
     <row r="48" spans="1:5" ht="15">
       <c r="A48" s="16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B48" s="8">
         <f>$B$36/12</f>
@@ -2311,31 +2319,31 @@
         <f t="shared" si="0"/>
         <v>943852</v>
       </c>
-      <c r="D48" s="24" t="s">
-        <v>113</v>
+      <c r="D48" s="27" t="s">
+        <v>114</v>
       </c>
       <c r="E48" s="26"/>
     </row>
     <row r="49" spans="1:5" ht="15">
       <c r="A49" s="18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B49" s="12">
         <f>SUM(B43:B48)</f>
-        <v>1772852</v>
+        <v>1805145.3333333333</v>
       </c>
       <c r="C49" s="12">
         <f>SUM(C43:C48)</f>
-        <v>21274224</v>
-      </c>
-      <c r="D49" s="27" t="s">
-        <v>114</v>
+        <v>21661744</v>
+      </c>
+      <c r="D49" s="28" t="s">
+        <v>115</v>
       </c>
       <c r="E49" s="26"/>
     </row>
     <row r="50" spans="1:5" ht="15">
       <c r="A50" s="16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B50" s="8">
         <f>B14/12</f>
@@ -2345,13 +2353,17 @@
         <f>B14</f>
         <v>18758948</v>
       </c>
-      <c r="D50" s="24" t="s">
-        <v>116</v>
+      <c r="D50" s="27" t="s">
+        <v>117</v>
       </c>
       <c r="E50" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="D43:E43"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="D50:E50"/>
     <mergeCell ref="D44:E44"/>
@@ -2368,10 +2380,6 @@
     <mergeCell ref="C39:E39"/>
     <mergeCell ref="D48:E48"/>
     <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="D43:E43"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/Weekends_2027年度予算_社長用.xlsx
+++ b/excel/Weekends_2027年度予算_社長用.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yataka-02\AppData\Local\Temp\claude\C--Users-yataka-02-Desktop-Claude\76fa42a7-01fc-42d8-86c7-11cf90447c56\scratchpad\margin-calculator\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBA0CE1-8426-4735-BD2F-86232BBF47E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{848066EE-3FB9-4D4F-A860-BA21858E973E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,10 +158,10 @@
     <t>年間目標との差</t>
   </si>
   <si>
-    <t>・売上目標と粗利目標は、店長がスマレジに登録した予算の比率で配分し、売上は10万円単位、粗利は5万円単位に丸めた。</t>
-  </si>
-  <si>
-    <t>・そのうえで、どの月も営業利益がマイナスにならないよう、閑散月（8・9・2・4・5・7月）を粗利180万円・売上530万円に引き上げた（毎月の販管費を賄うのに必要な粗利は約177万円）。目標を手で変えたら「年間目標との差」を0にする。</t>
+    <t>・月の目標は、赤字の月を減らしつつ無理のない伸びにそろえた。前年の売上が少ない月（8・9・2・4月）は前年の1.4倍まで引き上げ、残りの月は前年比が同じ（約1.09倍）になるよう配分。売上は10万円単位、粗利は5万円単位に丸めた。</t>
+  </si>
+  <si>
+    <t>・毎月の販管費を賄うのに必要な粗利は約177万円。8月・2月は前年の1.4倍でも届かず赤字、9月・4月はほぼトントン。目標を手で変えたら「年間目標との差」を0にする。</t>
   </si>
   <si>
     <t>・販管費と営業利益は、その月の粗利目標をちょうど達成し報奨金3万円を払った場合。販管費＝固定費（人件費・テナント固定分・その他の店舗経費・共通部の費用を12等分、月137.9万円）＋報奨金3万円＋テナント歩合（売上×6.92%）。内訳は「年間損益」シートの「4. 1か月の販管費」。</t>
@@ -206,7 +206,7 @@
     <t>売上高</t>
   </si>
   <si>
-    <t>予算は年6,860万円。105%は売上も5%増えた場合</t>
+    <t>予算は年6,300万円。105%は売上も5%増えた場合</t>
   </si>
   <si>
     <t>売上総利益（粗利）</t>
@@ -310,10 +310,10 @@
     <t>出所・備考</t>
   </si>
   <si>
-    <t>毎月黒字の案（2026-10-06。旧案は6,300万円）</t>
-  </si>
-  <si>
-    <t>毎月黒字の案（粗利率34.1%。旧案は2,150万円）</t>
+    <t>検討案（2026-10-07 月の目標をならした案）</t>
+  </si>
+  <si>
+    <t>検討案（粗利率34.1%）</t>
   </si>
   <si>
     <t>人件費（月）</t>
@@ -595,13 +595,13 @@
     </xf>
     <xf numFmtId="10" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -955,23 +955,23 @@
     <row r="4" spans="1:13" ht="24" customHeight="1">
       <c r="A4" s="4">
         <f>年間損益!C6</f>
-        <v>68600000</v>
+        <v>63000000</v>
       </c>
       <c r="B4" s="4">
         <f>年間損益!C7</f>
-        <v>23400000</v>
+        <v>21500000</v>
       </c>
       <c r="C4" s="5">
         <f>年間損益!C8</f>
-        <v>0.34110787172011664</v>
+        <v>0.34126984126984128</v>
       </c>
       <c r="D4" s="4">
         <f>年間損益!C15</f>
-        <v>1738256</v>
+        <v>225776</v>
       </c>
       <c r="E4" s="4">
         <f>年間損益!D15</f>
-        <v>2430900</v>
+        <v>842796</v>
       </c>
       <c r="F4" s="4">
         <f>年間損益!C10</f>
@@ -1038,26 +1038,26 @@
         <v>5.8333333333333334E-2</v>
       </c>
       <c r="E7" s="10">
-        <v>5300000</v>
+        <v>4200000</v>
       </c>
       <c r="F7" s="10">
-        <v>1800000</v>
+        <v>1450000</v>
       </c>
       <c r="G7" s="8">
         <f>ROUND(F7*年間損益!$B$38/50000,0)*50000</f>
-        <v>1900000</v>
+        <v>1500000</v>
       </c>
       <c r="H7" s="8">
         <f>E7*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1776312</v>
+        <v>1700192</v>
       </c>
       <c r="I7" s="8">
         <f t="shared" ref="I7:I18" si="1">F7-H7</f>
-        <v>23688</v>
+        <v>-250192</v>
       </c>
       <c r="J7" s="8">
         <f>SUM($I$7:I7)</f>
-        <v>23688</v>
+        <v>-250192</v>
       </c>
       <c r="K7" s="10"/>
       <c r="L7" s="9" t="str">
@@ -1084,26 +1084,26 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E8" s="10">
-        <v>5300000</v>
+        <v>5000000</v>
       </c>
       <c r="F8" s="10">
-        <v>1800000</v>
+        <v>1700000</v>
       </c>
       <c r="G8" s="8">
         <f>ROUND(F8*年間損益!$B$38/50000,0)*50000</f>
-        <v>1900000</v>
+        <v>1800000</v>
       </c>
       <c r="H8" s="8">
         <f>E8*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1776312</v>
+        <v>1755552</v>
       </c>
       <c r="I8" s="8">
         <f t="shared" si="1"/>
-        <v>23688</v>
+        <v>-55552</v>
       </c>
       <c r="J8" s="8">
         <f>SUM($I$7:I8)</f>
-        <v>47376</v>
+        <v>-305744</v>
       </c>
       <c r="K8" s="10"/>
       <c r="L8" s="9" t="str">
@@ -1130,26 +1130,26 @@
         <v>9.166666666666666E-2</v>
       </c>
       <c r="E9" s="10">
-        <v>5800000</v>
+        <v>5400000</v>
       </c>
       <c r="F9" s="10">
-        <v>2000000</v>
+        <v>1850000</v>
       </c>
       <c r="G9" s="8">
         <f>ROUND(F9*年間損益!$B$38/50000,0)*50000</f>
-        <v>2100000</v>
+        <v>1950000</v>
       </c>
       <c r="H9" s="8">
         <f>E9*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1810912</v>
+        <v>1783232</v>
       </c>
       <c r="I9" s="8">
         <f t="shared" si="1"/>
-        <v>189088</v>
+        <v>66768</v>
       </c>
       <c r="J9" s="8">
         <f>SUM($I$7:I9)</f>
-        <v>236464</v>
+        <v>-238976</v>
       </c>
       <c r="K9" s="10"/>
       <c r="L9" s="9" t="str">
@@ -1176,26 +1176,26 @@
         <v>9.166666666666666E-2</v>
       </c>
       <c r="E10" s="10">
-        <v>5800000</v>
+        <v>5600000</v>
       </c>
       <c r="F10" s="10">
-        <v>2000000</v>
+        <v>1900000</v>
       </c>
       <c r="G10" s="8">
         <f>ROUND(F10*年間損益!$B$38/50000,0)*50000</f>
-        <v>2100000</v>
+        <v>2000000</v>
       </c>
       <c r="H10" s="8">
         <f>E10*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1810912</v>
+        <v>1797072</v>
       </c>
       <c r="I10" s="8">
         <f t="shared" si="1"/>
-        <v>189088</v>
+        <v>102928</v>
       </c>
       <c r="J10" s="8">
         <f>SUM($I$7:I10)</f>
-        <v>425552</v>
+        <v>-136048</v>
       </c>
       <c r="K10" s="10"/>
       <c r="L10" s="9" t="str">
@@ -1222,26 +1222,26 @@
         <v>0.11666666666666667</v>
       </c>
       <c r="E11" s="10">
-        <v>7300000</v>
+        <v>7500000</v>
       </c>
       <c r="F11" s="10">
-        <v>2500000</v>
+        <v>2550000</v>
       </c>
       <c r="G11" s="8">
         <f>ROUND(F11*年間損益!$B$38/50000,0)*50000</f>
-        <v>2650000</v>
+        <v>2700000</v>
       </c>
       <c r="H11" s="8">
         <f>E11*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1914712</v>
+        <v>1928552</v>
       </c>
       <c r="I11" s="8">
         <f t="shared" si="1"/>
-        <v>585288</v>
+        <v>621448</v>
       </c>
       <c r="J11" s="8">
         <f>SUM($I$7:I11)</f>
-        <v>1010840</v>
+        <v>485400</v>
       </c>
       <c r="K11" s="10"/>
       <c r="L11" s="9" t="str">
@@ -1268,26 +1268,26 @@
         <v>0.1</v>
       </c>
       <c r="E12" s="10">
-        <v>6300000</v>
+        <v>5300000</v>
       </c>
       <c r="F12" s="10">
-        <v>2100000</v>
+        <v>1800000</v>
       </c>
       <c r="G12" s="8">
         <f>ROUND(F12*年間損益!$B$38/50000,0)*50000</f>
-        <v>2200000</v>
+        <v>1900000</v>
       </c>
       <c r="H12" s="8">
         <f>E12*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1845512</v>
+        <v>1776312</v>
       </c>
       <c r="I12" s="8">
         <f t="shared" si="1"/>
-        <v>254488</v>
+        <v>23688</v>
       </c>
       <c r="J12" s="8">
         <f>SUM($I$7:I12)</f>
-        <v>1265328</v>
+        <v>509088</v>
       </c>
       <c r="K12" s="10"/>
       <c r="L12" s="9" t="str">
@@ -1314,26 +1314,26 @@
         <v>5.8333333333333334E-2</v>
       </c>
       <c r="E13" s="10">
-        <v>5300000</v>
+        <v>3900000</v>
       </c>
       <c r="F13" s="10">
-        <v>1800000</v>
+        <v>1350000</v>
       </c>
       <c r="G13" s="8">
         <f>ROUND(F13*年間損益!$B$38/50000,0)*50000</f>
-        <v>1900000</v>
+        <v>1400000</v>
       </c>
       <c r="H13" s="8">
         <f>E13*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1776312</v>
+        <v>1679432</v>
       </c>
       <c r="I13" s="8">
         <f t="shared" si="1"/>
-        <v>23688</v>
+        <v>-329432</v>
       </c>
       <c r="J13" s="8">
         <f>SUM($I$7:I13)</f>
-        <v>1289016</v>
+        <v>179656</v>
       </c>
       <c r="K13" s="10"/>
       <c r="L13" s="9" t="str">
@@ -1360,26 +1360,26 @@
         <v>9.166666666666666E-2</v>
       </c>
       <c r="E14" s="10">
-        <v>5800000</v>
+        <v>5300000</v>
       </c>
       <c r="F14" s="10">
-        <v>2000000</v>
+        <v>1800000</v>
       </c>
       <c r="G14" s="8">
         <f>ROUND(F14*年間損益!$B$38/50000,0)*50000</f>
-        <v>2100000</v>
+        <v>1900000</v>
       </c>
       <c r="H14" s="8">
         <f>E14*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1810912</v>
+        <v>1776312</v>
       </c>
       <c r="I14" s="8">
         <f t="shared" si="1"/>
-        <v>189088</v>
+        <v>23688</v>
       </c>
       <c r="J14" s="8">
         <f>SUM($I$7:I14)</f>
-        <v>1478104</v>
+        <v>203344</v>
       </c>
       <c r="K14" s="10"/>
       <c r="L14" s="9" t="str">
@@ -1406,26 +1406,26 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E15" s="10">
-        <v>5300000</v>
+        <v>5000000</v>
       </c>
       <c r="F15" s="10">
-        <v>1800000</v>
+        <v>1700000</v>
       </c>
       <c r="G15" s="8">
         <f>ROUND(F15*年間損益!$B$38/50000,0)*50000</f>
-        <v>1900000</v>
+        <v>1800000</v>
       </c>
       <c r="H15" s="8">
         <f>E15*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1776312</v>
+        <v>1755552</v>
       </c>
       <c r="I15" s="8">
         <f t="shared" si="1"/>
-        <v>23688</v>
+        <v>-55552</v>
       </c>
       <c r="J15" s="8">
         <f>SUM($I$7:I15)</f>
-        <v>1501792</v>
+        <v>147792</v>
       </c>
       <c r="K15" s="10"/>
       <c r="L15" s="9" t="str">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J16" s="8">
         <f>SUM($I$7:I16)</f>
-        <v>1525480</v>
+        <v>171480</v>
       </c>
       <c r="K16" s="10"/>
       <c r="L16" s="9" t="str">
@@ -1498,26 +1498,26 @@
         <v>9.166666666666666E-2</v>
       </c>
       <c r="E17" s="10">
-        <v>5800000</v>
+        <v>5300000</v>
       </c>
       <c r="F17" s="10">
-        <v>2000000</v>
+        <v>1800000</v>
       </c>
       <c r="G17" s="8">
         <f>ROUND(F17*年間損益!$B$38/50000,0)*50000</f>
-        <v>2100000</v>
+        <v>1900000</v>
       </c>
       <c r="H17" s="8">
         <f>E17*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1810912</v>
+        <v>1776312</v>
       </c>
       <c r="I17" s="8">
         <f t="shared" si="1"/>
-        <v>189088</v>
+        <v>23688</v>
       </c>
       <c r="J17" s="8">
         <f>SUM($I$7:I17)</f>
-        <v>1714568</v>
+        <v>195168</v>
       </c>
       <c r="K17" s="10"/>
       <c r="L17" s="9" t="str">
@@ -1544,7 +1544,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="E18" s="10">
-        <v>5300000</v>
+        <v>5200000</v>
       </c>
       <c r="F18" s="10">
         <v>1800000</v>
@@ -1555,15 +1555,15 @@
       </c>
       <c r="H18" s="8">
         <f>E18*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1776312</v>
+        <v>1769392</v>
       </c>
       <c r="I18" s="8">
         <f t="shared" si="1"/>
-        <v>23688</v>
+        <v>30608</v>
       </c>
       <c r="J18" s="8">
         <f>SUM($I$7:I18)</f>
-        <v>1738256</v>
+        <v>225776</v>
       </c>
       <c r="K18" s="10"/>
       <c r="L18" s="9" t="str">
@@ -1593,23 +1593,23 @@
       </c>
       <c r="E19" s="12">
         <f t="shared" si="3"/>
-        <v>68600000</v>
+        <v>63000000</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="3"/>
-        <v>23400000</v>
+        <v>21500000</v>
       </c>
       <c r="G19" s="12">
         <f t="shared" si="3"/>
-        <v>24650000</v>
+        <v>22650000</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="3"/>
-        <v>21661744</v>
+        <v>21274224</v>
       </c>
       <c r="I19" s="12">
         <f t="shared" si="3"/>
-        <v>1738256</v>
+        <v>225776</v>
       </c>
       <c r="J19" s="14"/>
       <c r="K19" s="12">
@@ -1729,11 +1729,11 @@
       </c>
       <c r="C6" s="8">
         <f>$B$30</f>
-        <v>68600000</v>
+        <v>63000000</v>
       </c>
       <c r="D6" s="8">
         <f>$B$30*$B$38</f>
-        <v>72030000</v>
+        <v>66150000</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>51</v>
@@ -1748,11 +1748,11 @@
       </c>
       <c r="C7" s="12">
         <f>$B$31</f>
-        <v>23400000</v>
+        <v>21500000</v>
       </c>
       <c r="D7" s="12">
         <f>$B$31*$B$38</f>
-        <v>24570000</v>
+        <v>22575000</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>53</v>
@@ -1768,11 +1768,11 @@
       </c>
       <c r="C8" s="9">
         <f>C7/C6</f>
-        <v>0.34110787172011664</v>
+        <v>0.34126984126984128</v>
       </c>
       <c r="D8" s="9">
         <f>D7/D6</f>
-        <v>0.34110787172011664</v>
+        <v>0.34126984126984128</v>
       </c>
       <c r="E8" s="17"/>
     </row>
@@ -1823,11 +1823,11 @@
       </c>
       <c r="C11" s="8">
         <f>$B$33*12+C6*$B$34</f>
-        <v>7264624</v>
+        <v>6877104</v>
       </c>
       <c r="D11" s="8">
         <f>$B$33*12+D6*$B$34</f>
-        <v>7501980</v>
+        <v>7095084</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>59</v>
@@ -1881,11 +1881,11 @@
       </c>
       <c r="C14" s="8">
         <f>SUM(C9:C13)</f>
-        <v>21661744</v>
+        <v>21274224</v>
       </c>
       <c r="D14" s="8">
         <f>SUM(D9:D13)</f>
-        <v>22139100</v>
+        <v>21732204</v>
       </c>
       <c r="E14" s="17"/>
     </row>
@@ -1899,11 +1899,11 @@
       </c>
       <c r="C15" s="12">
         <f>C7-C14</f>
-        <v>1738256</v>
+        <v>225776</v>
       </c>
       <c r="D15" s="12">
         <f>D7-D14</f>
-        <v>2430900</v>
+        <v>842796</v>
       </c>
       <c r="E15" s="19"/>
     </row>
@@ -1936,11 +1936,11 @@
       </c>
       <c r="C17" s="12">
         <f>C15+C16</f>
-        <v>1438256</v>
+        <v>-74224</v>
       </c>
       <c r="D17" s="12">
         <f>D15+D16</f>
-        <v>2130900</v>
+        <v>542796</v>
       </c>
       <c r="E17" s="19"/>
     </row>
@@ -1951,11 +1951,11 @@
       <c r="B18" s="8"/>
       <c r="C18" s="8">
         <f>$B$39/($B$31/$B$30-$B$34)</f>
-        <v>60883209.79923743</v>
+        <v>60846964.598259076</v>
       </c>
       <c r="D18" s="8">
         <f>$B$39/($B$31/$B$30-$B$34)</f>
-        <v>60883209.79923743</v>
+        <v>60846964.598259076</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>70</v>
@@ -2065,7 +2065,7 @@
       <c r="B29" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C29" s="28" t="s">
         <v>84</v>
       </c>
       <c r="D29" s="25"/>
@@ -2076,9 +2076,9 @@
         <v>2</v>
       </c>
       <c r="B30" s="10">
-        <v>68600000</v>
-      </c>
-      <c r="C30" s="27" t="s">
+        <v>63000000</v>
+      </c>
+      <c r="C30" s="24" t="s">
         <v>85</v>
       </c>
       <c r="D30" s="25"/>
@@ -2089,9 +2089,9 @@
         <v>3</v>
       </c>
       <c r="B31" s="10">
-        <v>23400000</v>
-      </c>
-      <c r="C31" s="27" t="s">
+        <v>21500000</v>
+      </c>
+      <c r="C31" s="24" t="s">
         <v>86</v>
       </c>
       <c r="D31" s="25"/>
@@ -2104,7 +2104,7 @@
       <c r="B32" s="10">
         <v>800000</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="24" t="s">
         <v>88</v>
       </c>
       <c r="D32" s="25"/>
@@ -2117,7 +2117,7 @@
       <c r="B33" s="10">
         <v>209792</v>
       </c>
-      <c r="C33" s="27" t="s">
+      <c r="C33" s="24" t="s">
         <v>90</v>
       </c>
       <c r="D33" s="25"/>
@@ -2130,7 +2130,7 @@
       <c r="B34" s="22">
         <v>6.9199999999999998E-2</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="24" t="s">
         <v>92</v>
       </c>
       <c r="D34" s="25"/>
@@ -2143,7 +2143,7 @@
       <c r="B35" s="10">
         <v>3493268</v>
       </c>
-      <c r="C35" s="27" t="s">
+      <c r="C35" s="24" t="s">
         <v>94</v>
       </c>
       <c r="D35" s="25"/>
@@ -2156,7 +2156,7 @@
       <c r="B36" s="10">
         <v>943852</v>
       </c>
-      <c r="C36" s="27" t="s">
+      <c r="C36" s="24" t="s">
         <v>96</v>
       </c>
       <c r="D36" s="25"/>
@@ -2169,7 +2169,7 @@
       <c r="B37" s="10">
         <v>300000</v>
       </c>
-      <c r="C37" s="27" t="s">
+      <c r="C37" s="24" t="s">
         <v>98</v>
       </c>
       <c r="D37" s="25"/>
@@ -2182,7 +2182,7 @@
       <c r="B38" s="23">
         <v>1.05</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="C38" s="24" t="s">
         <v>100</v>
       </c>
       <c r="D38" s="25"/>
@@ -2196,7 +2196,7 @@
         <f>B32*12+B33*12+B35+B36</f>
         <v>16554624</v>
       </c>
-      <c r="C39" s="27" t="s">
+      <c r="C39" s="24" t="s">
         <v>102</v>
       </c>
       <c r="D39" s="25"/>
@@ -2217,7 +2217,7 @@
       <c r="C42" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D42" s="24" t="s">
+      <c r="D42" s="28" t="s">
         <v>106</v>
       </c>
       <c r="E42" s="26"/>
@@ -2234,7 +2234,7 @@
         <f t="shared" ref="C43:C48" si="0">B43*12</f>
         <v>9600000</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="D43" s="24" t="s">
         <v>107</v>
       </c>
       <c r="E43" s="26"/>
@@ -2251,7 +2251,7 @@
         <f t="shared" si="0"/>
         <v>360000</v>
       </c>
-      <c r="D44" s="27" t="s">
+      <c r="D44" s="24" t="s">
         <v>108</v>
       </c>
       <c r="E44" s="26"/>
@@ -2268,7 +2268,7 @@
         <f t="shared" si="0"/>
         <v>2517504</v>
       </c>
-      <c r="D45" s="27" t="s">
+      <c r="D45" s="24" t="s">
         <v>110</v>
       </c>
       <c r="E45" s="26"/>
@@ -2279,13 +2279,13 @@
       </c>
       <c r="B46" s="8">
         <f>$B$30*$B$34/12</f>
-        <v>395593.33333333331</v>
+        <v>363300</v>
       </c>
       <c r="C46" s="8">
         <f t="shared" si="0"/>
-        <v>4747120</v>
-      </c>
-      <c r="D46" s="27" t="s">
+        <v>4359600</v>
+      </c>
+      <c r="D46" s="24" t="s">
         <v>112</v>
       </c>
       <c r="E46" s="26"/>
@@ -2302,7 +2302,7 @@
         <f t="shared" si="0"/>
         <v>3493268</v>
       </c>
-      <c r="D47" s="27" t="s">
+      <c r="D47" s="24" t="s">
         <v>113</v>
       </c>
       <c r="E47" s="26"/>
@@ -2319,7 +2319,7 @@
         <f t="shared" si="0"/>
         <v>943852</v>
       </c>
-      <c r="D48" s="27" t="s">
+      <c r="D48" s="24" t="s">
         <v>114</v>
       </c>
       <c r="E48" s="26"/>
@@ -2330,13 +2330,13 @@
       </c>
       <c r="B49" s="12">
         <f>SUM(B43:B48)</f>
-        <v>1805145.3333333333</v>
+        <v>1772852</v>
       </c>
       <c r="C49" s="12">
         <f>SUM(C43:C48)</f>
-        <v>21661744</v>
-      </c>
-      <c r="D49" s="28" t="s">
+        <v>21274224</v>
+      </c>
+      <c r="D49" s="27" t="s">
         <v>115</v>
       </c>
       <c r="E49" s="26"/>
@@ -2353,17 +2353,13 @@
         <f>B14</f>
         <v>18758948</v>
       </c>
-      <c r="D50" s="27" t="s">
+      <c r="D50" s="24" t="s">
         <v>117</v>
       </c>
       <c r="E50" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="D43:E43"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="D50:E50"/>
     <mergeCell ref="D44:E44"/>
@@ -2380,6 +2376,10 @@
     <mergeCell ref="C39:E39"/>
     <mergeCell ref="D48:E48"/>
     <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="D43:E43"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/Weekends_2027年度予算_社長用.xlsx
+++ b/excel/Weekends_2027年度予算_社長用.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yataka-02\AppData\Local\Temp\claude\C--Users-yataka-02-Desktop-Claude\76fa42a7-01fc-42d8-86c7-11cf90447c56\scratchpad\margin-calculator\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{848066EE-3FB9-4D4F-A860-BA21858E973E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF462AA5-2080-4084-BCA6-E0D3FA75A2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="120">
   <si>
     <t>Weekends 2027年度　月別の目標と損益（2026年8月〜2027年7月）</t>
   </si>
@@ -42,29 +42,32 @@
     <t>金額は税抜・円。報奨金の判定はスマレジの粗利で行う。黄色の「実績粗利」を入れると、達成率と報奨金が出ます。</t>
   </si>
   <si>
-    <t>年間の売上目標</t>
-  </si>
-  <si>
-    <t>年間の粗利目標</t>
-  </si>
-  <si>
-    <t>粗利率</t>
+    <t>年間の予算
+（売上）</t>
+  </si>
+  <si>
+    <t>年間の予算
+（粗利）</t>
+  </si>
+  <si>
+    <t>月の目標の
+合計（粗利）</t>
+  </si>
+  <si>
+    <t>予算との差
+（上乗せ分）</t>
   </si>
   <si>
     <t>営業利益
-（全月100%達成）</t>
+（予算どおり）</t>
   </si>
   <si>
     <t>営業利益
-（全月105%達成）</t>
+（全月目標達成）</t>
   </si>
   <si>
     <t>報奨金・年
-（全月100%達成）</t>
-  </si>
-  <si>
-    <t>報奨金・年
-（全月105%達成）</t>
+（全月達成）</t>
   </si>
   <si>
     <t>月</t>
@@ -155,22 +158,19 @@
     <t>年計</t>
   </si>
   <si>
-    <t>年間目標との差</t>
-  </si>
-  <si>
-    <t>・月の目標は、赤字の月を減らしつつ無理のない伸びにそろえた。前年の売上が少ない月（8・9・2・4月）は前年の1.4倍まで引き上げ、残りの月は前年比が同じ（約1.09倍）になるよう配分。売上は10万円単位、粗利は5万円単位に丸めた。</t>
-  </si>
-  <si>
-    <t>・毎月の販管費を賄うのに必要な粗利は約177万円。8月・2月は前年の1.4倍でも届かず赤字、9月・4月はほぼトントン。目標を手で変えたら「年間目標との差」を0にする。</t>
-  </si>
-  <si>
-    <t>・販管費と営業利益は、その月の粗利目標をちょうど達成し報奨金3万円を払った場合。販管費＝固定費（人件費・テナント固定分・その他の店舗経費・共通部の費用を12等分、月137.9万円）＋報奨金3万円＋テナント歩合（売上×6.92%）。内訳は「年間損益」シートの「4. 1か月の販管費」。</t>
+    <t>年間予算との差</t>
+  </si>
+  <si>
+    <t>・月の目標＝店長がスマレジに登録した予算×粗利率（売上は店長の予算そのまま、粗利は5万円単位）。ただし、それでは営業利益が赤字になる月（8・9・2・4・5・7月）は、販管費を賄える粗利180万円・売上530万円に引き上げた。</t>
+  </si>
+  <si>
+    <t>・その結果、月の目標の合計（粗利2,285万円）は年間予算（2,150万円）より135万円多い。月の目標がいくつか未達でも年間予算には届く余裕になる。</t>
+  </si>
+  <si>
+    <t>・販管費と営業利益は、その月の粗利目標をちょうど達成し報奨金3万円を払った場合。販管費＝固定費（人件費・テナント固定分・その他の店舗経費・共通部の費用を12等分、月137.9万円）＋報奨金3万円＋テナント歩合（売上×6.92%）。</t>
   </si>
   <si>
     <t>・報奨金は、その月の粗利が粗利目標の100%以上で店舗計3万円、105%以上で5万円。1人あたりの額は「年間損益」シートの「2. 報奨金のルール」。</t>
-  </si>
-  <si>
-    <t>・105%の粗利目標は月ごとに5万円単位で丸めたため、年計は「年間損益」シートの105%欄（粗利目標×105%）と少しずれる。</t>
   </si>
   <si>
     <t>・達成率の年計は、実績を入れた月だけで計算する。</t>
@@ -193,11 +193,11 @@
   </si>
   <si>
     <t>2027年度予算
-（全月100%達成）</t>
-  </si>
-  <si>
-    <t>2027年度予算
-（全月105%達成）</t>
+（年間の予算どおり）</t>
+  </si>
+  <si>
+    <t>月の目標を
+全月達成した場合</t>
   </si>
   <si>
     <t>説明</t>
@@ -206,13 +206,16 @@
     <t>売上高</t>
   </si>
   <si>
-    <t>予算は年6,300万円。105%は売上も5%増えた場合</t>
+    <t>予算は年6,300万円。月の目標の合計は6,680万円（「月別目標」シートの年計）</t>
   </si>
   <si>
     <t>売上総利益（粗利）</t>
   </si>
   <si>
-    <t>前年は会計の粗利（棚卸の調整を含む）。報奨金の判定はスマレジの粗利で行う</t>
+    <t>予算は2,150万円、月の目標の合計は2,285万円。前年は会計の粗利（棚卸の調整を含む）</t>
+  </si>
+  <si>
+    <t>粗利率</t>
   </si>
   <si>
     <t>人件費（給与・賞与・法定福利）</t>
@@ -224,7 +227,7 @@
     <t>報奨金</t>
   </si>
   <si>
-    <t>全月達成した場合。下の「2. 報奨金のルール」から計算</t>
+    <t>全月で月3万円を支給した場合（予算の列も、利益を少なめに見るため全月支給と仮定）</t>
   </si>
   <si>
     <t>テナント経費</t>
@@ -310,7 +313,13 @@
     <t>出所・備考</t>
   </si>
   <si>
-    <t>検討案（2026-10-07 月の目標をならした案）</t>
+    <t>年間の売上目標</t>
+  </si>
+  <si>
+    <t>年間予算（決算上の目標）。月の目標の合計とは別</t>
+  </si>
+  <si>
+    <t>年間の粗利目標</t>
   </si>
   <si>
     <t>検討案（粗利率34.1%）</t>
@@ -364,7 +373,7 @@
     <t>人件費＋テナント固定分＋その他の店舗経費＋共通部の費用</t>
   </si>
   <si>
-    <t>4. 1か月の販管費（全月100%達成の場合）</t>
+    <t>4. 1か月の販管費（月の目標を全月達成した場合）</t>
   </si>
   <si>
     <t>1か月</t>
@@ -400,7 +409,7 @@
     <t>毎月同じ（前年は3月・7月の租税公課に集中。12等分している）</t>
   </si>
   <si>
-    <t>年間は「1. 年間の損益」の販管費 計（100%達成）と同じ</t>
+    <t>年間は「1. 年間の損益」の販管費 計（月の目標を全月達成）と同じ</t>
   </si>
   <si>
     <t>参考：前年実績（月平均）</t>
@@ -550,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -558,9 +567,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -907,7 +913,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -961,681 +967,681 @@
         <f>年間損益!C7</f>
         <v>21500000</v>
       </c>
-      <c r="C4" s="5">
-        <f>年間損益!C8</f>
-        <v>0.34126984126984128</v>
+      <c r="C4" s="4">
+        <f>F19</f>
+        <v>22850000</v>
       </c>
       <c r="D4" s="4">
+        <f>F20</f>
+        <v>1350000</v>
+      </c>
+      <c r="E4" s="4">
         <f>年間損益!C15</f>
         <v>225776</v>
       </c>
-      <c r="E4" s="4">
+      <c r="F4" s="4">
         <f>年間損益!D15</f>
-        <v>842796</v>
-      </c>
-      <c r="F4" s="4">
+        <v>1312816</v>
+      </c>
+      <c r="G4" s="4">
         <f>年間損益!C10</f>
         <v>360000</v>
       </c>
-      <c r="G4" s="4">
-        <f>年間損益!D10</f>
-        <v>600000</v>
-      </c>
     </row>
     <row r="6" spans="1:13" ht="52.05" customHeight="1">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>3040292</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>3500000</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <f t="shared" ref="D7:D18" si="0">C7/SUM($C$7:$C$18)</f>
         <v>5.8333333333333334E-2</v>
       </c>
-      <c r="E7" s="10">
-        <v>4200000</v>
-      </c>
-      <c r="F7" s="10">
-        <v>1450000</v>
-      </c>
-      <c r="G7" s="8">
+      <c r="E7" s="9">
+        <v>5300000</v>
+      </c>
+      <c r="F7" s="9">
+        <v>1800000</v>
+      </c>
+      <c r="G7" s="7">
         <f>ROUND(F7*年間損益!$B$38/50000,0)*50000</f>
-        <v>1500000</v>
-      </c>
-      <c r="H7" s="8">
+        <v>1900000</v>
+      </c>
+      <c r="H7" s="7">
         <f>E7*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1700192</v>
-      </c>
-      <c r="I7" s="8">
+        <v>1776312</v>
+      </c>
+      <c r="I7" s="7">
         <f t="shared" ref="I7:I18" si="1">F7-H7</f>
-        <v>-250192</v>
-      </c>
-      <c r="J7" s="8">
+        <v>23688</v>
+      </c>
+      <c r="J7" s="7">
         <f>SUM($I$7:I7)</f>
-        <v>-250192</v>
-      </c>
-      <c r="K7" s="10"/>
-      <c r="L7" s="9" t="str">
+        <v>23688</v>
+      </c>
+      <c r="K7" s="9"/>
+      <c r="L7" s="8" t="str">
         <f t="shared" ref="L7:L18" si="2">IF(K7="","",K7/F7)</f>
         <v/>
       </c>
-      <c r="M7" s="8" t="str">
+      <c r="M7" s="7" t="str">
         <f>IF(K7="","",IF(K7&gt;=G7,年間損益!$D$25,IF(K7&gt;=F7,年間損益!$C$25,0)))</f>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>3638478</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>4500000</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <f t="shared" si="0"/>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E8" s="10">
-        <v>5000000</v>
-      </c>
-      <c r="F8" s="10">
-        <v>1700000</v>
-      </c>
-      <c r="G8" s="8">
+      <c r="E8" s="9">
+        <v>5300000</v>
+      </c>
+      <c r="F8" s="9">
+        <v>1800000</v>
+      </c>
+      <c r="G8" s="7">
         <f>ROUND(F8*年間損益!$B$38/50000,0)*50000</f>
-        <v>1800000</v>
-      </c>
-      <c r="H8" s="8">
+        <v>1900000</v>
+      </c>
+      <c r="H8" s="7">
         <f>E8*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1755552</v>
-      </c>
-      <c r="I8" s="8">
+        <v>1776312</v>
+      </c>
+      <c r="I8" s="7">
         <f t="shared" si="1"/>
-        <v>-55552</v>
-      </c>
-      <c r="J8" s="8">
+        <v>23688</v>
+      </c>
+      <c r="J8" s="7">
         <f>SUM($I$7:I8)</f>
-        <v>-305744</v>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="9" t="str">
+        <v>47376</v>
+      </c>
+      <c r="K8" s="9"/>
+      <c r="L8" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M8" s="8" t="str">
+      <c r="M8" s="7" t="str">
         <f>IF(K8="","",IF(K8&gt;=G8,年間損益!$D$25,IF(K8&gt;=F8,年間損益!$C$25,0)))</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <v>4934704</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>5500000</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <f t="shared" si="0"/>
         <v>9.166666666666666E-2</v>
       </c>
-      <c r="E9" s="10">
-        <v>5400000</v>
-      </c>
-      <c r="F9" s="10">
-        <v>1850000</v>
-      </c>
-      <c r="G9" s="8">
+      <c r="E9" s="9">
+        <v>5500000</v>
+      </c>
+      <c r="F9" s="9">
+        <v>1900000</v>
+      </c>
+      <c r="G9" s="7">
         <f>ROUND(F9*年間損益!$B$38/50000,0)*50000</f>
-        <v>1950000</v>
-      </c>
-      <c r="H9" s="8">
+        <v>2000000</v>
+      </c>
+      <c r="H9" s="7">
         <f>E9*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1783232</v>
-      </c>
-      <c r="I9" s="8">
+        <v>1790152</v>
+      </c>
+      <c r="I9" s="7">
         <f t="shared" si="1"/>
-        <v>66768</v>
-      </c>
-      <c r="J9" s="8">
+        <v>109848</v>
+      </c>
+      <c r="J9" s="7">
         <f>SUM($I$7:I9)</f>
-        <v>-238976</v>
-      </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="9" t="str">
+        <v>157224</v>
+      </c>
+      <c r="K9" s="9"/>
+      <c r="L9" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M9" s="8" t="str">
+      <c r="M9" s="7" t="str">
         <f>IF(K9="","",IF(K9&gt;=G9,年間損益!$D$25,IF(K9&gt;=F9,年間損益!$C$25,0)))</f>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <v>5149749</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>5500000</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <f t="shared" si="0"/>
         <v>9.166666666666666E-2</v>
       </c>
-      <c r="E10" s="10">
-        <v>5600000</v>
-      </c>
-      <c r="F10" s="10">
+      <c r="E10" s="9">
+        <v>5500000</v>
+      </c>
+      <c r="F10" s="9">
         <v>1900000</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <f>ROUND(F10*年間損益!$B$38/50000,0)*50000</f>
         <v>2000000</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="7">
         <f>E10*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1797072</v>
-      </c>
-      <c r="I10" s="8">
+        <v>1790152</v>
+      </c>
+      <c r="I10" s="7">
         <f t="shared" si="1"/>
-        <v>102928</v>
-      </c>
-      <c r="J10" s="8">
+        <v>109848</v>
+      </c>
+      <c r="J10" s="7">
         <f>SUM($I$7:I10)</f>
-        <v>-136048</v>
-      </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="9" t="str">
+        <v>267072</v>
+      </c>
+      <c r="K10" s="9"/>
+      <c r="L10" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M10" s="8" t="str">
+      <c r="M10" s="7" t="str">
         <f>IF(K10="","",IF(K10&gt;=G10,年間損益!$D$25,IF(K10&gt;=F10,年間損益!$C$25,0)))</f>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>6820952</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>7000000</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <f t="shared" si="0"/>
         <v>0.11666666666666667</v>
       </c>
-      <c r="E11" s="10">
-        <v>7500000</v>
-      </c>
-      <c r="F11" s="10">
-        <v>2550000</v>
-      </c>
-      <c r="G11" s="8">
+      <c r="E11" s="9">
+        <v>7000000</v>
+      </c>
+      <c r="F11" s="9">
+        <v>2400000</v>
+      </c>
+      <c r="G11" s="7">
         <f>ROUND(F11*年間損益!$B$38/50000,0)*50000</f>
-        <v>2700000</v>
-      </c>
-      <c r="H11" s="8">
+        <v>2500000</v>
+      </c>
+      <c r="H11" s="7">
         <f>E11*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1928552</v>
-      </c>
-      <c r="I11" s="8">
+        <v>1893952</v>
+      </c>
+      <c r="I11" s="7">
         <f t="shared" si="1"/>
-        <v>621448</v>
-      </c>
-      <c r="J11" s="8">
+        <v>506048</v>
+      </c>
+      <c r="J11" s="7">
         <f>SUM($I$7:I11)</f>
-        <v>485400</v>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="9" t="str">
+        <v>773120</v>
+      </c>
+      <c r="K11" s="9"/>
+      <c r="L11" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M11" s="8" t="str">
+      <c r="M11" s="7" t="str">
         <f>IF(K11="","",IF(K11&gt;=G11,年間損益!$D$25,IF(K11&gt;=F11,年間損益!$C$25,0)))</f>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <v>4850701</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>6000000</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
+        <v>6000000</v>
+      </c>
+      <c r="F12" s="9">
+        <v>2050000</v>
+      </c>
+      <c r="G12" s="7">
+        <f>ROUND(F12*年間損益!$B$38/50000,0)*50000</f>
+        <v>2150000</v>
+      </c>
+      <c r="H12" s="7">
+        <f>E12*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1824752</v>
+      </c>
+      <c r="I12" s="7">
+        <f t="shared" si="1"/>
+        <v>225248</v>
+      </c>
+      <c r="J12" s="7">
+        <f>SUM($I$7:I12)</f>
+        <v>998368</v>
+      </c>
+      <c r="K12" s="9"/>
+      <c r="L12" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M12" s="7" t="str">
+        <f>IF(K12="","",IF(K12&gt;=G12,年間損益!$D$25,IF(K12&gt;=F12,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15">
+      <c r="A13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="7">
+        <v>2795656</v>
+      </c>
+      <c r="C13" s="7">
+        <v>3500000</v>
+      </c>
+      <c r="D13" s="8">
+        <f t="shared" si="0"/>
+        <v>5.8333333333333334E-2</v>
+      </c>
+      <c r="E13" s="9">
         <v>5300000</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F13" s="9">
         <v>1800000</v>
       </c>
-      <c r="G12" s="8">
-        <f>ROUND(F12*年間損益!$B$38/50000,0)*50000</f>
+      <c r="G13" s="7">
+        <f>ROUND(F13*年間損益!$B$38/50000,0)*50000</f>
         <v>1900000</v>
       </c>
-      <c r="H12" s="8">
-        <f>E12*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+      <c r="H13" s="7">
+        <f>E13*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
         <v>1776312</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I13" s="7">
         <f t="shared" si="1"/>
         <v>23688</v>
       </c>
-      <c r="J12" s="8">
-        <f>SUM($I$7:I12)</f>
-        <v>509088</v>
-      </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="9" t="str">
+      <c r="J13" s="7">
+        <f>SUM($I$7:I13)</f>
+        <v>1022056</v>
+      </c>
+      <c r="K13" s="9"/>
+      <c r="L13" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M12" s="8" t="str">
-        <f>IF(K12="","",IF(K12&gt;=G12,年間損益!$D$25,IF(K12&gt;=F12,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="15">
-      <c r="A13" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="8">
-        <v>2795656</v>
-      </c>
-      <c r="C13" s="8">
-        <v>3500000</v>
-      </c>
-      <c r="D13" s="9">
-        <f t="shared" si="0"/>
-        <v>5.8333333333333334E-2</v>
-      </c>
-      <c r="E13" s="10">
-        <v>3900000</v>
-      </c>
-      <c r="F13" s="10">
-        <v>1350000</v>
-      </c>
-      <c r="G13" s="8">
-        <f>ROUND(F13*年間損益!$B$38/50000,0)*50000</f>
-        <v>1400000</v>
-      </c>
-      <c r="H13" s="8">
-        <f>E13*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1679432</v>
-      </c>
-      <c r="I13" s="8">
-        <f t="shared" si="1"/>
-        <v>-329432</v>
-      </c>
-      <c r="J13" s="8">
-        <f>SUM($I$7:I13)</f>
-        <v>179656</v>
-      </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="M13" s="8" t="str">
+      <c r="M13" s="7" t="str">
         <f>IF(K13="","",IF(K13&gt;=G13,年間損益!$D$25,IF(K13&gt;=F13,年間損益!$C$25,0)))</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="7">
         <v>4419804</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>5500000</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <f t="shared" si="0"/>
         <v>9.166666666666666E-2</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
+        <v>5500000</v>
+      </c>
+      <c r="F14" s="9">
+        <v>1900000</v>
+      </c>
+      <c r="G14" s="7">
+        <f>ROUND(F14*年間損益!$B$38/50000,0)*50000</f>
+        <v>2000000</v>
+      </c>
+      <c r="H14" s="7">
+        <f>E14*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1790152</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="1"/>
+        <v>109848</v>
+      </c>
+      <c r="J14" s="7">
+        <f>SUM($I$7:I14)</f>
+        <v>1131904</v>
+      </c>
+      <c r="K14" s="9"/>
+      <c r="L14" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M14" s="7" t="str">
+        <f>IF(K14="","",IF(K14&gt;=G14,年間損益!$D$25,IF(K14&gt;=F14,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15">
+      <c r="A15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="7">
+        <v>3581469</v>
+      </c>
+      <c r="C15" s="7">
+        <v>4500000</v>
+      </c>
+      <c r="D15" s="8">
+        <f t="shared" si="0"/>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="E15" s="9">
         <v>5300000</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F15" s="9">
         <v>1800000</v>
       </c>
-      <c r="G14" s="8">
-        <f>ROUND(F14*年間損益!$B$38/50000,0)*50000</f>
+      <c r="G15" s="7">
+        <f>ROUND(F15*年間損益!$B$38/50000,0)*50000</f>
         <v>1900000</v>
       </c>
-      <c r="H14" s="8">
-        <f>E14*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+      <c r="H15" s="7">
+        <f>E15*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
         <v>1776312</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I15" s="7">
         <f t="shared" si="1"/>
         <v>23688</v>
       </c>
-      <c r="J14" s="8">
-        <f>SUM($I$7:I14)</f>
-        <v>203344</v>
-      </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="9" t="str">
+      <c r="J15" s="7">
+        <f>SUM($I$7:I15)</f>
+        <v>1155592</v>
+      </c>
+      <c r="K15" s="9"/>
+      <c r="L15" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M14" s="8" t="str">
-        <f>IF(K14="","",IF(K14&gt;=G14,年間損益!$D$25,IF(K14&gt;=F14,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="15">
-      <c r="A15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="8">
-        <v>3581469</v>
-      </c>
-      <c r="C15" s="8">
+      <c r="M15" s="7" t="str">
+        <f>IF(K15="","",IF(K15&gt;=G15,年間損益!$D$25,IF(K15&gt;=F15,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15">
+      <c r="A16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="7">
+        <v>4799124</v>
+      </c>
+      <c r="C16" s="7">
         <v>4500000</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D16" s="8">
         <f t="shared" si="0"/>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E15" s="10">
-        <v>5000000</v>
-      </c>
-      <c r="F15" s="10">
-        <v>1700000</v>
-      </c>
-      <c r="G15" s="8">
-        <f>ROUND(F15*年間損益!$B$38/50000,0)*50000</f>
+      <c r="E16" s="9">
+        <v>5300000</v>
+      </c>
+      <c r="F16" s="9">
         <v>1800000</v>
       </c>
-      <c r="H15" s="8">
-        <f>E15*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1755552</v>
-      </c>
-      <c r="I15" s="8">
+      <c r="G16" s="7">
+        <f>ROUND(F16*年間損益!$B$38/50000,0)*50000</f>
+        <v>1900000</v>
+      </c>
+      <c r="H16" s="7">
+        <f>E16*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1776312</v>
+      </c>
+      <c r="I16" s="7">
         <f t="shared" si="1"/>
-        <v>-55552</v>
-      </c>
-      <c r="J15" s="8">
-        <f>SUM($I$7:I15)</f>
-        <v>147792</v>
-      </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="9" t="str">
+        <v>23688</v>
+      </c>
+      <c r="J16" s="7">
+        <f>SUM($I$7:I16)</f>
+        <v>1179280</v>
+      </c>
+      <c r="K16" s="9"/>
+      <c r="L16" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M15" s="8" t="str">
-        <f>IF(K15="","",IF(K15&gt;=G15,年間損益!$D$25,IF(K15&gt;=F15,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="15">
-      <c r="A16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="8">
-        <v>4799124</v>
-      </c>
-      <c r="C16" s="8">
+      <c r="M16" s="7" t="str">
+        <f>IF(K16="","",IF(K16&gt;=G16,年間損益!$D$25,IF(K16&gt;=F16,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15">
+      <c r="A17" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="7">
+        <v>4888307</v>
+      </c>
+      <c r="C17" s="7">
+        <v>5500000</v>
+      </c>
+      <c r="D17" s="8">
+        <f t="shared" si="0"/>
+        <v>9.166666666666666E-2</v>
+      </c>
+      <c r="E17" s="9">
+        <v>5500000</v>
+      </c>
+      <c r="F17" s="9">
+        <v>1900000</v>
+      </c>
+      <c r="G17" s="7">
+        <f>ROUND(F17*年間損益!$B$38/50000,0)*50000</f>
+        <v>2000000</v>
+      </c>
+      <c r="H17" s="7">
+        <f>E17*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1790152</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="1"/>
+        <v>109848</v>
+      </c>
+      <c r="J17" s="7">
+        <f>SUM($I$7:I17)</f>
+        <v>1289128</v>
+      </c>
+      <c r="K17" s="9"/>
+      <c r="L17" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M17" s="7" t="str">
+        <f>IF(K17="","",IF(K17&gt;=G17,年間損益!$D$25,IF(K17&gt;=F17,年間損益!$C$25,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15">
+      <c r="A18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="7">
+        <v>4741065</v>
+      </c>
+      <c r="C18" s="7">
         <v>4500000</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D18" s="8">
         <f t="shared" si="0"/>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E18" s="9">
         <v>5300000</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F18" s="9">
         <v>1800000</v>
       </c>
-      <c r="G16" s="8">
-        <f>ROUND(F16*年間損益!$B$38/50000,0)*50000</f>
+      <c r="G18" s="7">
+        <f>ROUND(F18*年間損益!$B$38/50000,0)*50000</f>
         <v>1900000</v>
       </c>
-      <c r="H16" s="8">
-        <f>E16*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
+      <c r="H18" s="7">
+        <f>E18*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
         <v>1776312</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I18" s="7">
         <f t="shared" si="1"/>
         <v>23688</v>
       </c>
-      <c r="J16" s="8">
-        <f>SUM($I$7:I16)</f>
-        <v>171480</v>
-      </c>
-      <c r="K16" s="10"/>
-      <c r="L16" s="9" t="str">
+      <c r="J18" s="7">
+        <f>SUM($I$7:I18)</f>
+        <v>1312816</v>
+      </c>
+      <c r="K18" s="9"/>
+      <c r="L18" s="8" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M16" s="8" t="str">
-        <f>IF(K16="","",IF(K16&gt;=G16,年間損益!$D$25,IF(K16&gt;=F16,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="15">
-      <c r="A17" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="8">
-        <v>4888307</v>
-      </c>
-      <c r="C17" s="8">
-        <v>5500000</v>
-      </c>
-      <c r="D17" s="9">
-        <f t="shared" si="0"/>
-        <v>9.166666666666666E-2</v>
-      </c>
-      <c r="E17" s="10">
-        <v>5300000</v>
-      </c>
-      <c r="F17" s="10">
-        <v>1800000</v>
-      </c>
-      <c r="G17" s="8">
-        <f>ROUND(F17*年間損益!$B$38/50000,0)*50000</f>
-        <v>1900000</v>
-      </c>
-      <c r="H17" s="8">
-        <f>E17*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1776312</v>
-      </c>
-      <c r="I17" s="8">
-        <f t="shared" si="1"/>
-        <v>23688</v>
-      </c>
-      <c r="J17" s="8">
-        <f>SUM($I$7:I17)</f>
-        <v>195168</v>
-      </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="M17" s="8" t="str">
-        <f>IF(K17="","",IF(K17&gt;=G17,年間損益!$D$25,IF(K17&gt;=F17,年間損益!$C$25,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="15">
-      <c r="A18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="8">
-        <v>4741065</v>
-      </c>
-      <c r="C18" s="8">
-        <v>4500000</v>
-      </c>
-      <c r="D18" s="9">
-        <f t="shared" si="0"/>
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="E18" s="10">
-        <v>5200000</v>
-      </c>
-      <c r="F18" s="10">
-        <v>1800000</v>
-      </c>
-      <c r="G18" s="8">
-        <f>ROUND(F18*年間損益!$B$38/50000,0)*50000</f>
-        <v>1900000</v>
-      </c>
-      <c r="H18" s="8">
-        <f>E18*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1769392</v>
-      </c>
-      <c r="I18" s="8">
-        <f t="shared" si="1"/>
-        <v>30608</v>
-      </c>
-      <c r="J18" s="8">
-        <f>SUM($I$7:I18)</f>
-        <v>225776</v>
-      </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="M18" s="8" t="str">
+      <c r="M18" s="7" t="str">
         <f>IF(K18="","",IF(K18&gt;=G18,年間損益!$D$25,IF(K18&gt;=F18,年間損益!$C$25,0)))</f>
         <v/>
       </c>
     </row>
     <row r="19" spans="1:13" ht="15">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <f t="shared" ref="B19:I19" si="3">SUM(B7:B18)</f>
         <v>53660301</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <f t="shared" si="3"/>
         <v>60000000</v>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="12">
         <f t="shared" si="3"/>
         <v>0.99999999999999989</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="11">
         <f t="shared" si="3"/>
-        <v>63000000</v>
-      </c>
-      <c r="F19" s="12">
+        <v>66800000</v>
+      </c>
+      <c r="F19" s="11">
         <f t="shared" si="3"/>
-        <v>21500000</v>
-      </c>
-      <c r="G19" s="12">
+        <v>22850000</v>
+      </c>
+      <c r="G19" s="11">
         <f t="shared" si="3"/>
-        <v>22650000</v>
-      </c>
-      <c r="H19" s="12">
+        <v>24050000</v>
+      </c>
+      <c r="H19" s="11">
         <f t="shared" si="3"/>
-        <v>21274224</v>
-      </c>
-      <c r="I19" s="12">
+        <v>21537184</v>
+      </c>
+      <c r="I19" s="11">
         <f t="shared" si="3"/>
-        <v>225776</v>
-      </c>
-      <c r="J19" s="14"/>
-      <c r="K19" s="12">
+        <v>1312816</v>
+      </c>
+      <c r="J19" s="13"/>
+      <c r="K19" s="11">
         <f>SUM(K7:K18)</f>
         <v>0</v>
       </c>
-      <c r="L19" s="13" t="str">
+      <c r="L19" s="12" t="str">
         <f>IF(COUNT(K7:K18)=0,"",K19/SUMIF(K7:K18,"&lt;&gt;",F7:F18))</f>
         <v/>
       </c>
-      <c r="M19" s="12">
+      <c r="M19" s="11">
         <f>SUM(M7:M18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="7">
         <f>E19-年間損益!B30</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="8">
+        <v>3800000</v>
+      </c>
+      <c r="F20" s="7">
         <f>F19-年間損益!B31</f>
-        <v>0</v>
+        <v>1350000</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15">
@@ -1661,11 +1667,6 @@
     <row r="26" spans="1:13" ht="15">
       <c r="A26" s="2" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="15">
-      <c r="A27" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1690,673 +1691,673 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.600000000000001">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15">
       <c r="A2" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15">
+      <c r="A4" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15">
-      <c r="A4" s="15" t="s">
+    <row r="5" spans="1:5" ht="49.95" customHeight="1">
+      <c r="A5" s="5" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="49.95" customHeight="1">
-      <c r="A5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="15">
+      <c r="A6" s="15" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="15">
-      <c r="A6" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>53660301</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <f>$B$30</f>
         <v>63000000</v>
       </c>
-      <c r="D6" s="8">
-        <f>$B$30*$B$38</f>
-        <v>66150000</v>
-      </c>
-      <c r="E6" s="17" t="s">
+      <c r="D6" s="7">
+        <f>月別目標!$E$19</f>
+        <v>66800000</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="30">
+      <c r="A7" s="17" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="15">
-      <c r="A7" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <v>16612146</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <f>$B$31</f>
         <v>21500000</v>
       </c>
-      <c r="D7" s="12">
-        <f>$B$31*$B$38</f>
-        <v>22575000</v>
-      </c>
-      <c r="E7" s="19" t="s">
+      <c r="D7" s="11">
+        <f>月別目標!$F$19</f>
+        <v>22850000</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15">
+      <c r="A8" s="15" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="15">
-      <c r="A8" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="9">
+      <c r="B8" s="8">
         <f>B7/B6</f>
         <v>0.30957981394849055</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <f>C7/C6</f>
         <v>0.34126984126984128</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <f>D7/D6</f>
-        <v>0.34126984126984128</v>
-      </c>
-      <c r="E8" s="17"/>
+        <v>0.34206586826347307</v>
+      </c>
+      <c r="E8" s="16"/>
     </row>
     <row r="9" spans="1:5" ht="15">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <v>8091567</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <f>$B$32*12</f>
         <v>9600000</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <f>$B$32*12</f>
         <v>9600000</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="16" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15">
-      <c r="A10" s="16" t="s">
+    <row r="10" spans="1:5" ht="30">
+      <c r="A10" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <v>0</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <f>$C$25*12</f>
         <v>360000</v>
       </c>
-      <c r="D10" s="8">
-        <f>$D$25*12</f>
-        <v>600000</v>
-      </c>
-      <c r="E10" s="17" t="s">
+      <c r="D10" s="7">
+        <f>$C$25*12</f>
+        <v>360000</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>6230261</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <f>$B$33*12+C6*$B$34</f>
         <v>6877104</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <f>$B$33*12+D6*$B$34</f>
-        <v>7095084</v>
-      </c>
-      <c r="E11" s="17" t="s">
+        <v>7140064</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <v>3493268</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <f>$B$35</f>
         <v>3493268</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <f>$B$35</f>
         <v>3493268</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="16" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <v>943852</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <f>$B$36</f>
         <v>943852</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <f>$B$36</f>
         <v>943852</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="16" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="7">
         <f>SUM(B9:B13)</f>
         <v>18758948</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <f>SUM(C9:C13)</f>
         <v>21274224</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <f>SUM(D9:D13)</f>
-        <v>21732204</v>
-      </c>
-      <c r="E14" s="17"/>
+        <v>21537184</v>
+      </c>
+      <c r="E14" s="16"/>
     </row>
     <row r="15" spans="1:5" ht="15">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <f>B7-B14</f>
         <v>-2146802</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <f>C7-C14</f>
         <v>225776</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <f>D7-D14</f>
-        <v>842796</v>
-      </c>
-      <c r="E15" s="19"/>
+        <v>1312816</v>
+      </c>
+      <c r="E15" s="18"/>
     </row>
     <row r="16" spans="1:5" ht="30">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="7">
         <v>-153129</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <f>-$B$37</f>
         <v>-300000</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <f>-$B$37</f>
         <v>-300000</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="16" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <f>B15+B16</f>
         <v>-2299931</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <f>C15+C16</f>
         <v>-74224</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="11">
         <f>D15+D16</f>
-        <v>542796</v>
-      </c>
-      <c r="E17" s="19"/>
+        <v>1012816</v>
+      </c>
+      <c r="E17" s="18"/>
     </row>
     <row r="18" spans="1:5" ht="15">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7">
         <f>$B$39/($B$31/$B$30-$B$34)</f>
         <v>60846964.598259076</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <f>$B$39/($B$31/$B$30-$B$34)</f>
         <v>60846964.598259076</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="16" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="49.95" customHeight="1">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="5" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="19">
         <v>1</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <v>12000</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <v>20000</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="19">
         <v>1</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9">
         <v>8000</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <v>14000</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="19">
         <v>2</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="9">
         <v>5000</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="9">
         <v>8000</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="20">
         <f>SUM(B22:B24)</f>
         <v>4</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="11">
         <f>SUMPRODUCT($B$22:$B$24,C22:C24)</f>
         <v>30000</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="11">
         <f>SUMPRODUCT($B$22:$B$24,D22:D24)</f>
         <v>50000</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="8">
+      <c r="B26" s="15"/>
+      <c r="C26" s="7">
         <f>C25*12</f>
         <v>360000</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="7">
         <f>D25*12</f>
         <v>600000</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="14" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="25"/>
-      <c r="E29" s="26"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="25"/>
     </row>
     <row r="30" spans="1:5" ht="15">
-      <c r="A30" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="B30" s="10">
+      <c r="A30" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="9">
         <v>63000000</v>
       </c>
-      <c r="C30" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="D30" s="25"/>
-      <c r="E30" s="26"/>
+      <c r="C30" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" s="24"/>
+      <c r="E30" s="25"/>
     </row>
     <row r="31" spans="1:5" ht="15">
-      <c r="A31" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" s="10">
+      <c r="A31" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="9">
         <v>21500000</v>
       </c>
-      <c r="C31" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="D31" s="25"/>
-      <c r="E31" s="26"/>
+      <c r="C31" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" s="24"/>
+      <c r="E31" s="25"/>
     </row>
     <row r="32" spans="1:5" ht="15">
-      <c r="A32" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B32" s="10">
+      <c r="A32" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" s="9">
         <v>800000</v>
       </c>
-      <c r="C32" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" s="25"/>
-      <c r="E32" s="26"/>
+      <c r="C32" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="24"/>
+      <c r="E32" s="25"/>
     </row>
     <row r="33" spans="1:5" ht="15">
-      <c r="A33" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B33" s="10">
+      <c r="A33" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="9">
         <v>209792</v>
       </c>
-      <c r="C33" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="D33" s="25"/>
-      <c r="E33" s="26"/>
+      <c r="C33" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" s="24"/>
+      <c r="E33" s="25"/>
     </row>
     <row r="34" spans="1:5" ht="15">
-      <c r="A34" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="22">
+      <c r="A34" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="21">
         <v>6.9199999999999998E-2</v>
       </c>
-      <c r="C34" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="26"/>
+      <c r="C34" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="24"/>
+      <c r="E34" s="25"/>
     </row>
     <row r="35" spans="1:5" ht="15">
-      <c r="A35" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35" s="10">
+      <c r="A35" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="9">
         <v>3493268</v>
       </c>
-      <c r="C35" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" s="25"/>
-      <c r="E35" s="26"/>
+      <c r="C35" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" s="24"/>
+      <c r="E35" s="25"/>
     </row>
     <row r="36" spans="1:5" ht="15">
-      <c r="A36" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B36" s="10">
+      <c r="A36" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="9">
         <v>943852</v>
       </c>
-      <c r="C36" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D36" s="25"/>
-      <c r="E36" s="26"/>
+      <c r="C36" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36" s="24"/>
+      <c r="E36" s="25"/>
     </row>
     <row r="37" spans="1:5" ht="15">
-      <c r="A37" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B37" s="10">
+      <c r="A37" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="9">
         <v>300000</v>
       </c>
-      <c r="C37" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D37" s="25"/>
-      <c r="E37" s="26"/>
+      <c r="C37" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="24"/>
+      <c r="E37" s="25"/>
     </row>
     <row r="38" spans="1:5" ht="15">
-      <c r="A38" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B38" s="23">
+      <c r="A38" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="22">
         <v>1.05</v>
       </c>
-      <c r="C38" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="D38" s="25"/>
-      <c r="E38" s="26"/>
+      <c r="C38" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D38" s="24"/>
+      <c r="E38" s="25"/>
     </row>
     <row r="39" spans="1:5" ht="15">
-      <c r="A39" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B39" s="8">
+      <c r="A39" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="7">
         <f>B32*12+B33*12+B35+B36</f>
         <v>16554624</v>
       </c>
-      <c r="C39" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39" s="25"/>
-      <c r="E39" s="26"/>
+      <c r="C39" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" s="24"/>
+      <c r="E39" s="25"/>
     </row>
     <row r="41" spans="1:5" ht="15">
-      <c r="A41" s="15" t="s">
-        <v>103</v>
+      <c r="A41" s="14" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D42" s="28" t="s">
+      <c r="B42" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E42" s="26"/>
+      <c r="C42" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="E42" s="25"/>
     </row>
     <row r="43" spans="1:5" ht="15">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="7">
         <f>$B$32</f>
         <v>800000</v>
       </c>
-      <c r="C43" s="8">
+      <c r="C43" s="7">
         <f t="shared" ref="C43:C48" si="0">B43*12</f>
         <v>9600000</v>
       </c>
-      <c r="D43" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="E43" s="26"/>
+      <c r="D43" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E43" s="25"/>
     </row>
     <row r="44" spans="1:5" ht="15">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="7">
         <f>$C$25</f>
         <v>30000</v>
       </c>
-      <c r="C44" s="8">
+      <c r="C44" s="7">
         <f t="shared" si="0"/>
         <v>360000</v>
       </c>
-      <c r="D44" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="E44" s="26"/>
+      <c r="D44" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="E44" s="25"/>
     </row>
     <row r="45" spans="1:5" ht="15">
-      <c r="A45" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="B45" s="8">
+      <c r="A45" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" s="7">
         <f>$B$33</f>
         <v>209792</v>
       </c>
-      <c r="C45" s="8">
+      <c r="C45" s="7">
         <f t="shared" si="0"/>
         <v>2517504</v>
       </c>
-      <c r="D45" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="E45" s="26"/>
+      <c r="D45" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="E45" s="25"/>
     </row>
     <row r="46" spans="1:5" ht="15">
-      <c r="A46" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B46" s="8">
-        <f>$B$30*$B$34/12</f>
-        <v>363300</v>
-      </c>
-      <c r="C46" s="8">
+      <c r="A46" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" s="7">
+        <f>月別目標!$E$19*$B$34/12</f>
+        <v>385213.33333333331</v>
+      </c>
+      <c r="C46" s="7">
         <f t="shared" si="0"/>
-        <v>4359600</v>
-      </c>
-      <c r="D46" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="E46" s="26"/>
+        <v>4622560</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="E46" s="25"/>
     </row>
     <row r="47" spans="1:5" ht="15">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="7">
         <f>$B$35/12</f>
         <v>291105.66666666669</v>
       </c>
-      <c r="C47" s="8">
+      <c r="C47" s="7">
         <f t="shared" si="0"/>
         <v>3493268</v>
       </c>
-      <c r="D47" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="E47" s="26"/>
+      <c r="D47" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="E47" s="25"/>
     </row>
     <row r="48" spans="1:5" ht="15">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="7">
         <f>$B$36/12</f>
         <v>78654.333333333328</v>
       </c>
-      <c r="C48" s="8">
+      <c r="C48" s="7">
         <f t="shared" si="0"/>
         <v>943852</v>
       </c>
-      <c r="D48" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="E48" s="26"/>
+      <c r="D48" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="E48" s="25"/>
     </row>
     <row r="49" spans="1:5" ht="15">
-      <c r="A49" s="18" t="s">
+      <c r="A49" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B49" s="12">
+      <c r="B49" s="11">
         <f>SUM(B43:B48)</f>
-        <v>1772852</v>
-      </c>
-      <c r="C49" s="12">
+        <v>1794765.3333333333</v>
+      </c>
+      <c r="C49" s="11">
         <f>SUM(C43:C48)</f>
-        <v>21274224</v>
-      </c>
-      <c r="D49" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="E49" s="26"/>
+        <v>21537184</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="E49" s="25"/>
     </row>
     <row r="50" spans="1:5" ht="15">
-      <c r="A50" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B50" s="8">
+      <c r="A50" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B50" s="7">
         <f>B14/12</f>
         <v>1563245.6666666667</v>
       </c>
-      <c r="C50" s="8">
+      <c r="C50" s="7">
         <f>B14</f>
         <v>18758948</v>
       </c>
-      <c r="D50" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="E50" s="26"/>
+      <c r="D50" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E50" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/excel/Weekends_2027年度予算_社長用.xlsx
+++ b/excel/Weekends_2027年度予算_社長用.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yataka-02\AppData\Local\Temp\claude\C--Users-yataka-02-Desktop-Claude\76fa42a7-01fc-42d8-86c7-11cf90447c56\scratchpad\margin-calculator\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF462AA5-2080-4084-BCA6-E0D3FA75A2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819AFA66-CC0C-414B-AC7E-F18F510863CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="123">
   <si>
     <t>Weekends 2027年度　月別の目標と損益（2026年8月〜2027年7月）</t>
   </si>
@@ -167,7 +167,7 @@
     <t>・その結果、月の目標の合計（粗利2,285万円）は年間予算（2,150万円）より135万円多い。月の目標がいくつか未達でも年間予算には届く余裕になる。</t>
   </si>
   <si>
-    <t>・販管費と営業利益は、その月の粗利目標をちょうど達成し報奨金3万円を払った場合。販管費＝固定費（人件費・テナント固定分・その他の店舗経費・共通部の費用を12等分、月137.9万円）＋報奨金3万円＋テナント歩合（売上×6.92%）。</t>
+    <t>・販管費と営業利益は、その月の粗利目標をちょうど達成し報奨金3万円を払った場合。販管費は1万円単位＝固定費 月138万円（人件費80万・テナント固定分21万・その他の店舗経費29万・共通部の費用8万）＋報奨金3万円＋テナント歩合（売上×6.92%を1万円単位に丸め）。</t>
   </si>
   <si>
     <t>・報奨金は、その月の粗利が粗利目標の100%以上で店舗計3万円、105%以上で5万円。1人あたりの額は「年間損益」シートの「2. 報奨金のルール」。</t>
@@ -233,19 +233,19 @@
     <t>テナント経費</t>
   </si>
   <si>
-    <t>売上歩合制：固定分（月）×12＋売上×連動率</t>
+    <t>売上歩合制：固定分月21万円×12＋売上×6.92%（歩合は月ごとに1万円単位に丸め）</t>
   </si>
   <si>
     <t>その他の店舗経費</t>
   </si>
   <si>
-    <t>管理諸費・減価償却・旅費・通信・消耗品など（発展会計 営業部）</t>
+    <t>予算は月29万円（前年3,493,268円を丸め）。管理諸費・減価償却・旅費・通信・消耗品など</t>
   </si>
   <si>
     <t>共通部の費用</t>
   </si>
   <si>
-    <t>租税公課882,500（3月・7月）、消耗品・保険料など。中身は確認中</t>
+    <t>予算は月8万円（前年943,852円を丸め）。前年は租税公課882,500（3月・7月）など。中身は確認中</t>
   </si>
   <si>
     <t>販管費 計</t>
@@ -334,25 +334,25 @@
     <t>テナント経費の固定分（月）</t>
   </si>
   <si>
-    <t>前年12か月の実績から算出（売上歩合制の固定部分）</t>
+    <t>前年12か月の実績から算出した209,792円を丸め（売上歩合制の固定部分）</t>
   </si>
   <si>
     <t>テナント経費の売上連動率</t>
   </si>
   <si>
-    <t>同上（売上に比例する部分）</t>
+    <t>同上（売上に比例する部分）。月の歩合は1万円単位に丸める</t>
   </si>
   <si>
     <t>その他の店舗経費（年）</t>
   </si>
   <si>
-    <t>前年実績（発展会計 営業部）</t>
+    <t>月29万円×12。前年実績3,493,268円（発展会計 営業部）を丸め</t>
   </si>
   <si>
     <t>共通部の費用（年）</t>
   </si>
   <si>
-    <t>前年実績（発展会計 全社−営業部）</t>
+    <t>月8万円×12。前年実績943,852円（発展会計 全社−営業部）を丸め</t>
   </si>
   <si>
     <t>営業外費用（年）</t>
@@ -373,10 +373,23 @@
     <t>人件費＋テナント固定分＋その他の店舗経費＋共通部の費用</t>
   </si>
   <si>
-    <t>4. 1か月の販管費（月の目標を全月達成した場合）</t>
-  </si>
-  <si>
-    <t>1か月</t>
+    <t>4. 1か月の販管費（月の目標を全月達成した場合・1万円単位）</t>
+  </si>
+  <si>
+    <t>売上530万円の月
+（8・9・2・4・5・7月）</t>
+  </si>
+  <si>
+    <t>売上550万円の月
+（10・11・3・6月）</t>
+  </si>
+  <si>
+    <t>1月
+（売上600万円）</t>
+  </si>
+  <si>
+    <t>12月
+（売上700万円）</t>
   </si>
   <si>
     <t>年間</t>
@@ -385,37 +398,37 @@
     <t>決まり方</t>
   </si>
   <si>
-    <t>毎月同じ（賞与も12等分して含めている）</t>
-  </si>
-  <si>
-    <t>粗利目標を達成した月だけ。105%以上なら5万円</t>
+    <t>毎月80万円（賞与も12等分して含めている）</t>
+  </si>
+  <si>
+    <t>粗利目標を達成した月だけ3万円。105%以上なら5万円</t>
   </si>
   <si>
     <t>テナント経費（固定分）</t>
   </si>
   <si>
-    <t>毎月同じ</t>
+    <t>毎月21万円</t>
   </si>
   <si>
     <t>テナント経費（売上歩合）</t>
   </si>
   <si>
-    <t>売上×6.92%。月の売上で変わる（ここは12か月の平均。月別は「月別目標」シートの販管費の列）</t>
-  </si>
-  <si>
-    <t>毎月同じ（前年実績の12等分）</t>
-  </si>
-  <si>
-    <t>毎月同じ（前年は3月・7月の租税公課に集中。12等分している）</t>
+    <t>売上×6.92%を1万円単位に丸め。売上の大きい月ほど増える</t>
+  </si>
+  <si>
+    <t>毎月29万円</t>
+  </si>
+  <si>
+    <t>毎月8万円（前年は3月・7月の租税公課に集中。12等分している）</t>
   </si>
   <si>
     <t>年間は「1. 年間の損益」の販管費 計（月の目標を全月達成）と同じ</t>
   </si>
   <si>
-    <t>参考：前年実績（月平均）</t>
-  </si>
-  <si>
-    <t>前年は月119万円（8月）〜234万円（7月）。賞与（12月・7月）と租税公課（3月・7月）の月に増える</t>
+    <t>参考：前年実績</t>
+  </si>
+  <si>
+    <t>月平均156万円。月119万円（8月）〜234万円（7月）。賞与（12月・7月）と租税公課（3月・7月）の月に増える</t>
   </si>
 </sst>
 </file>
@@ -559,7 +572,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -601,10 +614,17 @@
     </xf>
     <xf numFmtId="10" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -977,11 +997,11 @@
       </c>
       <c r="E4" s="4">
         <f>年間損益!C15</f>
-        <v>225776</v>
+        <v>220000</v>
       </c>
       <c r="F4" s="4">
         <f>年間損益!D15</f>
-        <v>1312816</v>
+        <v>1290000</v>
       </c>
       <c r="G4" s="4">
         <f>年間損益!C10</f>
@@ -1054,16 +1074,16 @@
         <v>1900000</v>
       </c>
       <c r="H7" s="7">
-        <f>E7*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1776312</v>
+        <f>ROUND(E7*年間損益!$B$34,-4)+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1780000</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" ref="I7:I18" si="1">F7-H7</f>
-        <v>23688</v>
+        <v>20000</v>
       </c>
       <c r="J7" s="7">
         <f>SUM($I$7:I7)</f>
-        <v>23688</v>
+        <v>20000</v>
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="8" t="str">
@@ -1100,16 +1120,16 @@
         <v>1900000</v>
       </c>
       <c r="H8" s="7">
-        <f>E8*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1776312</v>
+        <f>ROUND(E8*年間損益!$B$34,-4)+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1780000</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" si="1"/>
-        <v>23688</v>
+        <v>20000</v>
       </c>
       <c r="J8" s="7">
         <f>SUM($I$7:I8)</f>
-        <v>47376</v>
+        <v>40000</v>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="8" t="str">
@@ -1146,16 +1166,16 @@
         <v>2000000</v>
       </c>
       <c r="H9" s="7">
-        <f>E9*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1790152</v>
+        <f>ROUND(E9*年間損益!$B$34,-4)+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1790000</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" si="1"/>
-        <v>109848</v>
+        <v>110000</v>
       </c>
       <c r="J9" s="7">
         <f>SUM($I$7:I9)</f>
-        <v>157224</v>
+        <v>150000</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="8" t="str">
@@ -1192,16 +1212,16 @@
         <v>2000000</v>
       </c>
       <c r="H10" s="7">
-        <f>E10*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1790152</v>
+        <f>ROUND(E10*年間損益!$B$34,-4)+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1790000</v>
       </c>
       <c r="I10" s="7">
         <f t="shared" si="1"/>
-        <v>109848</v>
+        <v>110000</v>
       </c>
       <c r="J10" s="7">
         <f>SUM($I$7:I10)</f>
-        <v>267072</v>
+        <v>260000</v>
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="8" t="str">
@@ -1238,16 +1258,16 @@
         <v>2500000</v>
       </c>
       <c r="H11" s="7">
-        <f>E11*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1893952</v>
+        <f>ROUND(E11*年間損益!$B$34,-4)+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1890000</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" si="1"/>
-        <v>506048</v>
+        <v>510000</v>
       </c>
       <c r="J11" s="7">
         <f>SUM($I$7:I11)</f>
-        <v>773120</v>
+        <v>770000</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="8" t="str">
@@ -1284,16 +1304,16 @@
         <v>2150000</v>
       </c>
       <c r="H12" s="7">
-        <f>E12*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1824752</v>
+        <f>ROUND(E12*年間損益!$B$34,-4)+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1830000</v>
       </c>
       <c r="I12" s="7">
         <f t="shared" si="1"/>
-        <v>225248</v>
+        <v>220000</v>
       </c>
       <c r="J12" s="7">
         <f>SUM($I$7:I12)</f>
-        <v>998368</v>
+        <v>990000</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="8" t="str">
@@ -1330,16 +1350,16 @@
         <v>1900000</v>
       </c>
       <c r="H13" s="7">
-        <f>E13*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1776312</v>
+        <f>ROUND(E13*年間損益!$B$34,-4)+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1780000</v>
       </c>
       <c r="I13" s="7">
         <f t="shared" si="1"/>
-        <v>23688</v>
+        <v>20000</v>
       </c>
       <c r="J13" s="7">
         <f>SUM($I$7:I13)</f>
-        <v>1022056</v>
+        <v>1010000</v>
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="8" t="str">
@@ -1376,16 +1396,16 @@
         <v>2000000</v>
       </c>
       <c r="H14" s="7">
-        <f>E14*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1790152</v>
+        <f>ROUND(E14*年間損益!$B$34,-4)+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1790000</v>
       </c>
       <c r="I14" s="7">
         <f t="shared" si="1"/>
-        <v>109848</v>
+        <v>110000</v>
       </c>
       <c r="J14" s="7">
         <f>SUM($I$7:I14)</f>
-        <v>1131904</v>
+        <v>1120000</v>
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="8" t="str">
@@ -1422,16 +1442,16 @@
         <v>1900000</v>
       </c>
       <c r="H15" s="7">
-        <f>E15*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1776312</v>
+        <f>ROUND(E15*年間損益!$B$34,-4)+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1780000</v>
       </c>
       <c r="I15" s="7">
         <f t="shared" si="1"/>
-        <v>23688</v>
+        <v>20000</v>
       </c>
       <c r="J15" s="7">
         <f>SUM($I$7:I15)</f>
-        <v>1155592</v>
+        <v>1140000</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="8" t="str">
@@ -1468,16 +1488,16 @@
         <v>1900000</v>
       </c>
       <c r="H16" s="7">
-        <f>E16*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1776312</v>
+        <f>ROUND(E16*年間損益!$B$34,-4)+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1780000</v>
       </c>
       <c r="I16" s="7">
         <f t="shared" si="1"/>
-        <v>23688</v>
+        <v>20000</v>
       </c>
       <c r="J16" s="7">
         <f>SUM($I$7:I16)</f>
-        <v>1179280</v>
+        <v>1160000</v>
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="8" t="str">
@@ -1514,16 +1534,16 @@
         <v>2000000</v>
       </c>
       <c r="H17" s="7">
-        <f>E17*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1790152</v>
+        <f>ROUND(E17*年間損益!$B$34,-4)+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1790000</v>
       </c>
       <c r="I17" s="7">
         <f t="shared" si="1"/>
-        <v>109848</v>
+        <v>110000</v>
       </c>
       <c r="J17" s="7">
         <f>SUM($I$7:I17)</f>
-        <v>1289128</v>
+        <v>1270000</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="8" t="str">
@@ -1560,16 +1580,16 @@
         <v>1900000</v>
       </c>
       <c r="H18" s="7">
-        <f>E18*年間損益!$B$34+年間損益!$B$39/12+年間損益!$C$25</f>
-        <v>1776312</v>
+        <f>ROUND(E18*年間損益!$B$34,-4)+年間損益!$B$39/12+年間損益!$C$25</f>
+        <v>1780000</v>
       </c>
       <c r="I18" s="7">
         <f t="shared" si="1"/>
-        <v>23688</v>
+        <v>20000</v>
       </c>
       <c r="J18" s="7">
         <f>SUM($I$7:I18)</f>
-        <v>1312816</v>
+        <v>1290000</v>
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="8" t="str">
@@ -1611,11 +1631,11 @@
       </c>
       <c r="H19" s="11">
         <f t="shared" si="3"/>
-        <v>21537184</v>
+        <v>21560000</v>
       </c>
       <c r="I19" s="11">
         <f t="shared" si="3"/>
-        <v>1312816</v>
+        <v>1290000</v>
       </c>
       <c r="J19" s="13"/>
       <c r="K19" s="11">
@@ -1681,30 +1701,30 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="72" customWidth="1"/>
+    <col min="2" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="56" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.600000000000001">
+    <row r="1" spans="1:7" ht="18.600000000000001">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15">
+    <row r="2" spans="1:7" ht="15">
       <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15">
+    <row r="4" spans="1:7" ht="15">
       <c r="A4" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="49.95" customHeight="1">
+    <row r="5" spans="1:7" ht="49.95" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>44</v>
       </c>
@@ -1717,11 +1737,13 @@
       <c r="D5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="30" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="15">
+      <c r="F5" s="24"/>
+      <c r="G5" s="25"/>
+    </row>
+    <row r="6" spans="1:7" ht="15">
       <c r="A6" s="15" t="s">
         <v>49</v>
       </c>
@@ -1736,11 +1758,13 @@
         <f>月別目標!$E$19</f>
         <v>66800000</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="23" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="30">
+      <c r="F6" s="24"/>
+      <c r="G6" s="25"/>
+    </row>
+    <row r="7" spans="1:7" ht="30" customHeight="1">
       <c r="A7" s="17" t="s">
         <v>51</v>
       </c>
@@ -1755,11 +1779,13 @@
         <f>月別目標!$F$19</f>
         <v>22850000</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="27" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="15">
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
+    </row>
+    <row r="8" spans="1:7" ht="15">
       <c r="A8" s="15" t="s">
         <v>53</v>
       </c>
@@ -1775,9 +1801,11 @@
         <f>D7/D6</f>
         <v>0.34206586826347307</v>
       </c>
-      <c r="E8" s="16"/>
-    </row>
-    <row r="9" spans="1:5" ht="15">
+      <c r="E8" s="23"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="25"/>
+    </row>
+    <row r="9" spans="1:7" ht="30" customHeight="1">
       <c r="A9" s="15" t="s">
         <v>54</v>
       </c>
@@ -1792,11 +1820,13 @@
         <f>$B$32*12</f>
         <v>9600000</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="23" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="30">
+      <c r="F9" s="24"/>
+      <c r="G9" s="25"/>
+    </row>
+    <row r="10" spans="1:7" ht="15">
       <c r="A10" s="15" t="s">
         <v>56</v>
       </c>
@@ -1811,11 +1841,13 @@
         <f>$C$25*12</f>
         <v>360000</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="23" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="15">
+      <c r="F10" s="24"/>
+      <c r="G10" s="25"/>
+    </row>
+    <row r="11" spans="1:7" ht="15">
       <c r="A11" s="15" t="s">
         <v>58</v>
       </c>
@@ -1823,18 +1855,20 @@
         <v>6230261</v>
       </c>
       <c r="C11" s="7">
-        <f>$B$33*12+C6*$B$34</f>
-        <v>6877104</v>
+        <f>$B$33*12+ROUND(C6*$B$34,-4)</f>
+        <v>6880000</v>
       </c>
       <c r="D11" s="7">
-        <f>$B$33*12+D6*$B$34</f>
-        <v>7140064</v>
-      </c>
-      <c r="E11" s="16" t="s">
+        <f>$B$33*12+SUMPRODUCT(ROUND(月別目標!$E$7:$E$18*$B$34,-4))</f>
+        <v>7160000</v>
+      </c>
+      <c r="E11" s="23" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="15">
+      <c r="F11" s="24"/>
+      <c r="G11" s="25"/>
+    </row>
+    <row r="12" spans="1:7" ht="30" customHeight="1">
       <c r="A12" s="15" t="s">
         <v>60</v>
       </c>
@@ -1843,17 +1877,19 @@
       </c>
       <c r="C12" s="7">
         <f>$B$35</f>
-        <v>3493268</v>
+        <v>3480000</v>
       </c>
       <c r="D12" s="7">
         <f>$B$35</f>
-        <v>3493268</v>
-      </c>
-      <c r="E12" s="16" t="s">
+        <v>3480000</v>
+      </c>
+      <c r="E12" s="23" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="15">
+      <c r="F12" s="24"/>
+      <c r="G12" s="25"/>
+    </row>
+    <row r="13" spans="1:7" ht="30" customHeight="1">
       <c r="A13" s="15" t="s">
         <v>62</v>
       </c>
@@ -1862,17 +1898,19 @@
       </c>
       <c r="C13" s="7">
         <f>$B$36</f>
-        <v>943852</v>
+        <v>960000</v>
       </c>
       <c r="D13" s="7">
         <f>$B$36</f>
-        <v>943852</v>
-      </c>
-      <c r="E13" s="16" t="s">
+        <v>960000</v>
+      </c>
+      <c r="E13" s="23" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="15">
+      <c r="F13" s="24"/>
+      <c r="G13" s="25"/>
+    </row>
+    <row r="14" spans="1:7" ht="15">
       <c r="A14" s="15" t="s">
         <v>64</v>
       </c>
@@ -1882,15 +1920,17 @@
       </c>
       <c r="C14" s="7">
         <f>SUM(C9:C13)</f>
-        <v>21274224</v>
+        <v>21280000</v>
       </c>
       <c r="D14" s="7">
         <f>SUM(D9:D13)</f>
-        <v>21537184</v>
-      </c>
-      <c r="E14" s="16"/>
-    </row>
-    <row r="15" spans="1:5" ht="15">
+        <v>21560000</v>
+      </c>
+      <c r="E14" s="23"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="25"/>
+    </row>
+    <row r="15" spans="1:7" ht="15">
       <c r="A15" s="17" t="s">
         <v>65</v>
       </c>
@@ -1900,15 +1940,17 @@
       </c>
       <c r="C15" s="11">
         <f>C7-C14</f>
-        <v>225776</v>
+        <v>220000</v>
       </c>
       <c r="D15" s="11">
         <f>D7-D14</f>
-        <v>1312816</v>
-      </c>
-      <c r="E15" s="18"/>
-    </row>
-    <row r="16" spans="1:5" ht="30">
+        <v>1290000</v>
+      </c>
+      <c r="E15" s="27"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="29"/>
+    </row>
+    <row r="16" spans="1:7" ht="15">
       <c r="A16" s="15" t="s">
         <v>66</v>
       </c>
@@ -1923,11 +1965,13 @@
         <f>-$B$37</f>
         <v>-300000</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="23" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="15">
+      <c r="F16" s="24"/>
+      <c r="G16" s="25"/>
+    </row>
+    <row r="17" spans="1:7" ht="15">
       <c r="A17" s="17" t="s">
         <v>68</v>
       </c>
@@ -1937,37 +1981,41 @@
       </c>
       <c r="C17" s="11">
         <f>C15+C16</f>
-        <v>-74224</v>
+        <v>-80000</v>
       </c>
       <c r="D17" s="11">
         <f>D15+D16</f>
-        <v>1012816</v>
-      </c>
-      <c r="E17" s="18"/>
-    </row>
-    <row r="18" spans="1:5" ht="15">
+        <v>990000</v>
+      </c>
+      <c r="E17" s="27"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="29"/>
+    </row>
+    <row r="18" spans="1:7" ht="15">
       <c r="A18" s="15" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7">
         <f>$B$39/($B$31/$B$30-$B$34)</f>
-        <v>60846964.598259076</v>
+        <v>60866724.230473027</v>
       </c>
       <c r="D18" s="7">
         <f>$B$39/($B$31/$B$30-$B$34)</f>
-        <v>60846964.598259076</v>
-      </c>
-      <c r="E18" s="16" t="s">
+        <v>60866724.230473027</v>
+      </c>
+      <c r="E18" s="23" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="15">
+      <c r="F18" s="24"/>
+      <c r="G18" s="25"/>
+    </row>
+    <row r="20" spans="1:7" ht="15">
       <c r="A20" s="14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="49.95" customHeight="1">
+    <row r="21" spans="1:7" ht="49.95" customHeight="1">
       <c r="A21" s="5" t="s">
         <v>72</v>
       </c>
@@ -1981,7 +2029,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15">
+    <row r="22" spans="1:7" ht="15">
       <c r="A22" s="15" t="s">
         <v>76</v>
       </c>
@@ -1995,7 +2043,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15">
+    <row r="23" spans="1:7" ht="15">
       <c r="A23" s="15" t="s">
         <v>77</v>
       </c>
@@ -2009,7 +2057,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15">
+    <row r="24" spans="1:7" ht="15">
       <c r="A24" s="15" t="s">
         <v>78</v>
       </c>
@@ -2023,7 +2071,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15">
+    <row r="25" spans="1:7" ht="15">
       <c r="A25" s="17" t="s">
         <v>79</v>
       </c>
@@ -2040,7 +2088,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15">
+    <row r="26" spans="1:7" ht="15">
       <c r="A26" s="15" t="s">
         <v>80</v>
       </c>
@@ -2054,161 +2102,183 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15">
+    <row r="28" spans="1:7" ht="15">
       <c r="A28" s="14" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15">
+    <row r="29" spans="1:7" ht="15">
       <c r="A29" s="5" t="s">
         <v>82</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="30" t="s">
         <v>84</v>
       </c>
       <c r="D29" s="24"/>
-      <c r="E29" s="25"/>
-    </row>
-    <row r="30" spans="1:5" ht="15">
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="25"/>
+    </row>
+    <row r="30" spans="1:7" ht="15">
       <c r="A30" s="15" t="s">
         <v>85</v>
       </c>
       <c r="B30" s="9">
         <v>63000000</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="26" t="s">
         <v>86</v>
       </c>
       <c r="D30" s="24"/>
-      <c r="E30" s="25"/>
-    </row>
-    <row r="31" spans="1:5" ht="15">
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="25"/>
+    </row>
+    <row r="31" spans="1:7" ht="15">
       <c r="A31" s="15" t="s">
         <v>87</v>
       </c>
       <c r="B31" s="9">
         <v>21500000</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="26" t="s">
         <v>88</v>
       </c>
       <c r="D31" s="24"/>
-      <c r="E31" s="25"/>
-    </row>
-    <row r="32" spans="1:5" ht="15">
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="25"/>
+    </row>
+    <row r="32" spans="1:7" ht="15">
       <c r="A32" s="15" t="s">
         <v>89</v>
       </c>
       <c r="B32" s="9">
         <v>800000</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="26" t="s">
         <v>90</v>
       </c>
       <c r="D32" s="24"/>
-      <c r="E32" s="25"/>
-    </row>
-    <row r="33" spans="1:5" ht="15">
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="25"/>
+    </row>
+    <row r="33" spans="1:7" ht="15">
       <c r="A33" s="15" t="s">
         <v>91</v>
       </c>
       <c r="B33" s="9">
-        <v>209792</v>
-      </c>
-      <c r="C33" s="23" t="s">
+        <v>210000</v>
+      </c>
+      <c r="C33" s="26" t="s">
         <v>92</v>
       </c>
       <c r="D33" s="24"/>
-      <c r="E33" s="25"/>
-    </row>
-    <row r="34" spans="1:5" ht="15">
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="25"/>
+    </row>
+    <row r="34" spans="1:7" ht="15">
       <c r="A34" s="15" t="s">
         <v>93</v>
       </c>
       <c r="B34" s="21">
         <v>6.9199999999999998E-2</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="26" t="s">
         <v>94</v>
       </c>
       <c r="D34" s="24"/>
-      <c r="E34" s="25"/>
-    </row>
-    <row r="35" spans="1:5" ht="15">
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="25"/>
+    </row>
+    <row r="35" spans="1:7" ht="15">
       <c r="A35" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B35" s="9">
-        <v>3493268</v>
-      </c>
-      <c r="C35" s="23" t="s">
+        <v>3480000</v>
+      </c>
+      <c r="C35" s="26" t="s">
         <v>96</v>
       </c>
       <c r="D35" s="24"/>
-      <c r="E35" s="25"/>
-    </row>
-    <row r="36" spans="1:5" ht="15">
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="25"/>
+    </row>
+    <row r="36" spans="1:7" ht="15">
       <c r="A36" s="15" t="s">
         <v>97</v>
       </c>
       <c r="B36" s="9">
-        <v>943852</v>
-      </c>
-      <c r="C36" s="23" t="s">
+        <v>960000</v>
+      </c>
+      <c r="C36" s="26" t="s">
         <v>98</v>
       </c>
       <c r="D36" s="24"/>
-      <c r="E36" s="25"/>
-    </row>
-    <row r="37" spans="1:5" ht="15">
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="25"/>
+    </row>
+    <row r="37" spans="1:7" ht="15">
       <c r="A37" s="15" t="s">
         <v>99</v>
       </c>
       <c r="B37" s="9">
         <v>300000</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C37" s="26" t="s">
         <v>100</v>
       </c>
       <c r="D37" s="24"/>
-      <c r="E37" s="25"/>
-    </row>
-    <row r="38" spans="1:5" ht="15">
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="25"/>
+    </row>
+    <row r="38" spans="1:7" ht="15">
       <c r="A38" s="15" t="s">
         <v>101</v>
       </c>
       <c r="B38" s="22">
         <v>1.05</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="26" t="s">
         <v>102</v>
       </c>
       <c r="D38" s="24"/>
-      <c r="E38" s="25"/>
-    </row>
-    <row r="39" spans="1:5" ht="15">
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="25"/>
+    </row>
+    <row r="39" spans="1:7" ht="15">
       <c r="A39" s="15" t="s">
         <v>103</v>
       </c>
       <c r="B39" s="7">
         <f>B32*12+B33*12+B35+B36</f>
-        <v>16554624</v>
-      </c>
-      <c r="C39" s="23" t="s">
+        <v>16560000</v>
+      </c>
+      <c r="C39" s="26" t="s">
         <v>104</v>
       </c>
       <c r="D39" s="24"/>
-      <c r="E39" s="25"/>
-    </row>
-    <row r="41" spans="1:5" ht="15">
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="25"/>
+    </row>
+    <row r="41" spans="1:7" ht="15">
       <c r="A41" s="14" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15">
+    <row r="42" spans="1:7" ht="49.95" customHeight="1">
       <c r="A42" s="5" t="s">
         <v>82</v>
       </c>
@@ -2218,12 +2288,20 @@
       <c r="C42" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D42" s="27" t="s">
+      <c r="D42" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E42" s="25"/>
-    </row>
-    <row r="43" spans="1:5" ht="15">
+      <c r="E42" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15">
       <c r="A43" s="15" t="s">
         <v>54</v>
       </c>
@@ -2232,15 +2310,26 @@
         <v>800000</v>
       </c>
       <c r="C43" s="7">
-        <f t="shared" ref="C43:C48" si="0">B43*12</f>
+        <f>$B$32</f>
+        <v>800000</v>
+      </c>
+      <c r="D43" s="7">
+        <f>$B$32</f>
+        <v>800000</v>
+      </c>
+      <c r="E43" s="7">
+        <f>$B$32</f>
+        <v>800000</v>
+      </c>
+      <c r="F43" s="7">
+        <f>B43*12</f>
         <v>9600000</v>
       </c>
-      <c r="D43" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E43" s="25"/>
-    </row>
-    <row r="44" spans="1:5" ht="15">
+      <c r="G43" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15">
       <c r="A44" s="15" t="s">
         <v>56</v>
       </c>
@@ -2249,138 +2338,208 @@
         <v>30000</v>
       </c>
       <c r="C44" s="7">
-        <f t="shared" si="0"/>
+        <f>$C$25</f>
+        <v>30000</v>
+      </c>
+      <c r="D44" s="7">
+        <f>$C$25</f>
+        <v>30000</v>
+      </c>
+      <c r="E44" s="7">
+        <f>$C$25</f>
+        <v>30000</v>
+      </c>
+      <c r="F44" s="7">
+        <f>B44*12</f>
         <v>360000</v>
       </c>
-      <c r="D44" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="E44" s="25"/>
-    </row>
-    <row r="45" spans="1:5" ht="15">
+      <c r="G44" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15">
       <c r="A45" s="15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B45" s="7">
         <f>$B$33</f>
-        <v>209792</v>
+        <v>210000</v>
       </c>
       <c r="C45" s="7">
-        <f t="shared" si="0"/>
-        <v>2517504</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="E45" s="25"/>
-    </row>
-    <row r="46" spans="1:5" ht="15">
+        <f>$B$33</f>
+        <v>210000</v>
+      </c>
+      <c r="D45" s="7">
+        <f>$B$33</f>
+        <v>210000</v>
+      </c>
+      <c r="E45" s="7">
+        <f>$B$33</f>
+        <v>210000</v>
+      </c>
+      <c r="F45" s="7">
+        <f>B45*12</f>
+        <v>2520000</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15">
       <c r="A46" s="15" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B46" s="7">
-        <f>月別目標!$E$19*$B$34/12</f>
-        <v>385213.33333333331</v>
+        <f>ROUND(月別目標!E7*$B$34,-4)</f>
+        <v>370000</v>
       </c>
       <c r="C46" s="7">
-        <f t="shared" si="0"/>
-        <v>4622560</v>
-      </c>
-      <c r="D46" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="E46" s="25"/>
-    </row>
-    <row r="47" spans="1:5" ht="15">
+        <f>ROUND(月別目標!E9*$B$34,-4)</f>
+        <v>380000</v>
+      </c>
+      <c r="D46" s="7">
+        <f>ROUND(月別目標!E12*$B$34,-4)</f>
+        <v>420000</v>
+      </c>
+      <c r="E46" s="7">
+        <f>ROUND(月別目標!E11*$B$34,-4)</f>
+        <v>480000</v>
+      </c>
+      <c r="F46" s="7">
+        <f>SUMPRODUCT(ROUND(月別目標!$E$7:$E$18*$B$34,-4))</f>
+        <v>4640000</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15">
       <c r="A47" s="15" t="s">
         <v>60</v>
       </c>
       <c r="B47" s="7">
         <f>$B$35/12</f>
-        <v>291105.66666666669</v>
+        <v>290000</v>
       </c>
       <c r="C47" s="7">
-        <f t="shared" si="0"/>
-        <v>3493268</v>
-      </c>
-      <c r="D47" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="E47" s="25"/>
-    </row>
-    <row r="48" spans="1:5" ht="15">
+        <f>$B$35/12</f>
+        <v>290000</v>
+      </c>
+      <c r="D47" s="7">
+        <f>$B$35/12</f>
+        <v>290000</v>
+      </c>
+      <c r="E47" s="7">
+        <f>$B$35/12</f>
+        <v>290000</v>
+      </c>
+      <c r="F47" s="7">
+        <f>B47*12</f>
+        <v>3480000</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="30">
       <c r="A48" s="15" t="s">
         <v>62</v>
       </c>
       <c r="B48" s="7">
         <f>$B$36/12</f>
-        <v>78654.333333333328</v>
+        <v>80000</v>
       </c>
       <c r="C48" s="7">
-        <f t="shared" si="0"/>
-        <v>943852</v>
-      </c>
-      <c r="D48" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="E48" s="25"/>
-    </row>
-    <row r="49" spans="1:5" ht="15">
+        <f>$B$36/12</f>
+        <v>80000</v>
+      </c>
+      <c r="D48" s="7">
+        <f>$B$36/12</f>
+        <v>80000</v>
+      </c>
+      <c r="E48" s="7">
+        <f>$B$36/12</f>
+        <v>80000</v>
+      </c>
+      <c r="F48" s="7">
+        <f>B48*12</f>
+        <v>960000</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="30">
       <c r="A49" s="17" t="s">
         <v>64</v>
       </c>
       <c r="B49" s="11">
         <f>SUM(B43:B48)</f>
-        <v>1794765.3333333333</v>
+        <v>1780000</v>
       </c>
       <c r="C49" s="11">
         <f>SUM(C43:C48)</f>
-        <v>21537184</v>
-      </c>
-      <c r="D49" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="E49" s="25"/>
-    </row>
-    <row r="50" spans="1:5" ht="15">
+        <v>1790000</v>
+      </c>
+      <c r="D49" s="11">
+        <f>SUM(D43:D48)</f>
+        <v>1830000</v>
+      </c>
+      <c r="E49" s="11">
+        <f>SUM(E43:E48)</f>
+        <v>1890000</v>
+      </c>
+      <c r="F49" s="11">
+        <f>SUM(F43:F48)</f>
+        <v>21560000</v>
+      </c>
+      <c r="G49" s="18" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="30" customHeight="1">
       <c r="A50" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B50" s="7">
-        <f>B14/12</f>
-        <v>1563245.6666666667</v>
-      </c>
-      <c r="C50" s="7">
+        <v>121</v>
+      </c>
+      <c r="B50" s="15"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="7">
         <f>B14</f>
         <v>18758948</v>
       </c>
-      <c r="D50" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E50" s="25"/>
+      <c r="G50" s="16" t="s">
+        <v>122</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="D43:E43"/>
+  <mergeCells count="25">
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="C33:G33"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/Weekends_2027年度予算_社長用.xlsx
+++ b/excel/Weekends_2027年度予算_社長用.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yataka-02\AppData\Local\Temp\claude\C--Users-yataka-02-Desktop-Claude\76fa42a7-01fc-42d8-86c7-11cf90447c56\scratchpad\margin-calculator\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819AFA66-CC0C-414B-AC7E-F18F510863CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550753F3-2FF7-40EE-9AE3-55E8667116E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="月別目標" sheetId="1" r:id="rId1"/>
+    <sheet name="報奨金の目標" sheetId="1" r:id="rId1"/>
     <sheet name="年間損益" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -36,7 +36,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="123">
   <si>
-    <t>Weekends 2027年度　月別の目標と損益（2026年8月〜2027年7月）</t>
+    <t>Weekends 2027年度　月別の報奨金の目標と損益（2026年8月〜2027年7月）</t>
   </si>
   <si>
     <t>金額は税抜・円。報奨金の判定はスマレジの粗利で行う。黄色の「実績粗利」を入れると、達成率と報奨金が出ます。</t>
@@ -50,7 +50,7 @@
 （粗利）</t>
   </si>
   <si>
-    <t>月の目標の
+    <t>報奨金の目標の
 合計（粗利）</t>
   </si>
   <si>
@@ -161,10 +161,10 @@
     <t>年間予算との差</t>
   </si>
   <si>
-    <t>・月の目標＝店長がスマレジに登録した予算×粗利率（売上は店長の予算そのまま、粗利は5万円単位）。ただし、それでは営業利益が赤字になる月（8・9・2・4・5・7月）は、販管費を賄える粗利180万円・売上530万円に引き上げた。</t>
-  </si>
-  <si>
-    <t>・その結果、月の目標の合計（粗利2,285万円）は年間予算（2,150万円）より135万円多い。月の目標がいくつか未達でも年間予算には届く余裕になる。</t>
+    <t>・報奨金の目標＝店長がスマレジに登録した予算×粗利率（売上は店長の予算そのまま、粗利は5万円単位）。ただし、それでは営業利益が赤字になる月（8・9・2・4・5・7月）は、販管費を賄える粗利180万円・売上530万円に引き上げた。</t>
+  </si>
+  <si>
+    <t>・その結果、報奨金の目標の合計（粗利2,285万円）は年間予算（2,150万円）より135万円多い。報奨金の目標がいくつか未達でも年間予算には届く余裕になる。</t>
   </si>
   <si>
     <t>・販管費と営業利益は、その月の粗利目標をちょうど達成し報奨金3万円を払った場合。販管費は1万円単位＝固定費 月138万円（人件費80万・テナント固定分21万・その他の店舗経費29万・共通部の費用8万）＋報奨金3万円＋テナント歩合（売上×6.92%を1万円単位に丸め）。</t>
@@ -196,7 +196,7 @@
 （年間の予算どおり）</t>
   </si>
   <si>
-    <t>月の目標を
+    <t>報奨金の目標を
 全月達成した場合</t>
   </si>
   <si>
@@ -206,13 +206,13 @@
     <t>売上高</t>
   </si>
   <si>
-    <t>予算は年6,300万円。月の目標の合計は6,680万円（「月別目標」シートの年計）</t>
+    <t>予算は年6,300万円。報奨金の目標の合計は6,680万円（「報奨金の目標」シートの年計）</t>
   </si>
   <si>
     <t>売上総利益（粗利）</t>
   </si>
   <si>
-    <t>予算は2,150万円、月の目標の合計は2,285万円。前年は会計の粗利（棚卸の調整を含む）</t>
+    <t>予算は2,150万円、報奨金の目標の合計は2,285万円。前年は会計の粗利（棚卸の調整を含む）</t>
   </si>
   <si>
     <t>粗利率</t>
@@ -316,7 +316,7 @@
     <t>年間の売上目標</t>
   </si>
   <si>
-    <t>年間予算（決算上の目標）。月の目標の合計とは別</t>
+    <t>年間予算（決算上の目標）。報奨金の目標の合計とは別</t>
   </si>
   <si>
     <t>年間の粗利目標</t>
@@ -373,7 +373,7 @@
     <t>人件費＋テナント固定分＋その他の店舗経費＋共通部の費用</t>
   </si>
   <si>
-    <t>4. 1か月の販管費（月の目標を全月達成した場合・1万円単位）</t>
+    <t>4. 1か月の販管費（報奨金の目標を全月達成した場合・1万円単位）</t>
   </si>
   <si>
     <t>売上530万円の月
@@ -422,7 +422,7 @@
     <t>毎月8万円（前年は3月・7月の租税公課に集中。12等分している）</t>
   </si>
   <si>
-    <t>年間は「1. 年間の損益」の販管費 計（月の目標を全月達成）と同じ</t>
+    <t>年間は「1. 年間の損益」の販管費 計（報奨金の目標を全月達成）と同じ</t>
   </si>
   <si>
     <t>参考：前年実績</t>
@@ -1743,7 +1743,7 @@
       <c r="F5" s="24"/>
       <c r="G5" s="25"/>
     </row>
-    <row r="6" spans="1:7" ht="15">
+    <row r="6" spans="1:7" ht="30" customHeight="1">
       <c r="A6" s="15" t="s">
         <v>49</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>63000000</v>
       </c>
       <c r="D6" s="7">
-        <f>月別目標!$E$19</f>
+        <f>報奨金の目標!$E$19</f>
         <v>66800000</v>
       </c>
       <c r="E6" s="23" t="s">
@@ -1776,7 +1776,7 @@
         <v>21500000</v>
       </c>
       <c r="D7" s="11">
-        <f>月別目標!$F$19</f>
+        <f>報奨金の目標!$F$19</f>
         <v>22850000</v>
       </c>
       <c r="E7" s="27" t="s">
@@ -1859,7 +1859,7 @@
         <v>6880000</v>
       </c>
       <c r="D11" s="7">
-        <f>$B$33*12+SUMPRODUCT(ROUND(月別目標!$E$7:$E$18*$B$34,-4))</f>
+        <f>$B$33*12+SUMPRODUCT(ROUND(報奨金の目標!$E$7:$E$18*$B$34,-4))</f>
         <v>7160000</v>
       </c>
       <c r="E11" s="23" t="s">
@@ -2390,23 +2390,23 @@
         <v>116</v>
       </c>
       <c r="B46" s="7">
-        <f>ROUND(月別目標!E7*$B$34,-4)</f>
+        <f>ROUND(報奨金の目標!E7*$B$34,-4)</f>
         <v>370000</v>
       </c>
       <c r="C46" s="7">
-        <f>ROUND(月別目標!E9*$B$34,-4)</f>
+        <f>ROUND(報奨金の目標!E9*$B$34,-4)</f>
         <v>380000</v>
       </c>
       <c r="D46" s="7">
-        <f>ROUND(月別目標!E12*$B$34,-4)</f>
+        <f>ROUND(報奨金の目標!E12*$B$34,-4)</f>
         <v>420000</v>
       </c>
       <c r="E46" s="7">
-        <f>ROUND(月別目標!E11*$B$34,-4)</f>
+        <f>ROUND(報奨金の目標!E11*$B$34,-4)</f>
         <v>480000</v>
       </c>
       <c r="F46" s="7">
-        <f>SUMPRODUCT(ROUND(月別目標!$E$7:$E$18*$B$34,-4))</f>
+        <f>SUMPRODUCT(ROUND(報奨金の目標!$E$7:$E$18*$B$34,-4))</f>
         <v>4640000</v>
       </c>
       <c r="G46" s="16" t="s">
